--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY112"/>
+  <dimension ref="A1:AY114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12844,6 +12844,218 @@
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>114785373</v>
+      </c>
+      <c r="B113" t="n">
+        <v>90237</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Kårsta_SO_Bergsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>685296</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6616647</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Amelie Lindhagen</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Amelie Lindhagen</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr">
+        <is>
+          <t>Stora Obrutna Skogsområden</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>114785451</v>
+      </c>
+      <c r="B114" t="n">
+        <v>90517</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>658</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Kårsta_SO_Bergsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>685292</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6616645</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Amelie Lindhagen</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Amelie Lindhagen</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr">
+        <is>
+          <t>Stora Obrutna Skogsområden</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY114"/>
+  <dimension ref="A1:AY119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13056,6 +13056,526 @@
         </is>
       </c>
     </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114831778</v>
+      </c>
+      <c r="B115" t="n">
+        <v>90258</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Barrnaturskog nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>685293</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6616740</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2024-02-24</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2024-02-24</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>114831522</v>
+      </c>
+      <c r="B116" t="n">
+        <v>90204</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>685253</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6616744</v>
+      </c>
+      <c r="S116" t="n">
+        <v>15</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2024-02-24</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2024-02-24</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>114832853</v>
+      </c>
+      <c r="B117" t="n">
+        <v>57251</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Barrnaturskog nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>685288</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6616770</v>
+      </c>
+      <c r="S117" t="n">
+        <v>10</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2024-02-24</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2024-02-24</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>114831900</v>
+      </c>
+      <c r="B118" t="n">
+        <v>57251</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>685331</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6616715</v>
+      </c>
+      <c r="S118" t="n">
+        <v>20</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2024-02-24</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2024-02-24</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>114832279</v>
+      </c>
+      <c r="B119" t="n">
+        <v>90258</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>685376</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6616749</v>
+      </c>
+      <c r="S119" t="n">
+        <v>20</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2024-02-24</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2024-02-24</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY119"/>
+  <dimension ref="A1:AY120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
@@ -13576,6 +13576,120 @@
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>114856949</v>
+      </c>
+      <c r="B120" t="n">
+        <v>90902</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>898</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Blackticka</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Steccherinum collabens</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Barrnaturskog nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>685306</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6616655</v>
+      </c>
+      <c r="S120" t="n">
+        <v>10</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF120" t="inlineStr"/>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY120"/>
+  <dimension ref="A1:AY122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13690,6 +13690,222 @@
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>114868347</v>
+      </c>
+      <c r="B121" t="n">
+        <v>90929</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>685300</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6616683</v>
+      </c>
+      <c r="S121" t="n">
+        <v>20</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>114885708</v>
+      </c>
+      <c r="B122" t="n">
+        <v>74534</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>685332</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6616647</v>
+      </c>
+      <c r="S122" t="n">
+        <v>15</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2024-02-26</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2024-02-26</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY122"/>
+  <dimension ref="A1:AY124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13906,6 +13906,229 @@
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>114999533</v>
+      </c>
+      <c r="B123" t="n">
+        <v>94182</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>210</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>685333</v>
+      </c>
+      <c r="R123" t="n">
+        <v>6616685</v>
+      </c>
+      <c r="S123" t="n">
+        <v>20</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>114999680</v>
+      </c>
+      <c r="B124" t="n">
+        <v>74608</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>308</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Barrnaturskog nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>685335</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6616662</v>
+      </c>
+      <c r="S124" t="n">
+        <v>10</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>På undersidan av granlåga.</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF124" t="inlineStr"/>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY124"/>
+  <dimension ref="A1:AY126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14129,6 +14129,206 @@
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>115031352</v>
+      </c>
+      <c r="B125" t="n">
+        <v>96514</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>685317</v>
+      </c>
+      <c r="R125" t="n">
+        <v>6616684</v>
+      </c>
+      <c r="S125" t="n">
+        <v>20</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>115031254</v>
+      </c>
+      <c r="B126" t="n">
+        <v>74611</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>308</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Gransumpskog nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>685365</v>
+      </c>
+      <c r="R126" t="n">
+        <v>6616656</v>
+      </c>
+      <c r="S126" t="n">
+        <v>10</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY126"/>
+  <dimension ref="A1:AY127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13578,10 +13578,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>114856949</v>
+        <v>114831924</v>
       </c>
       <c r="B120" t="n">
-        <v>90902</v>
+        <v>57597</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13590,52 +13590,47 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>898</v>
+        <v>103015</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Barrnaturskog nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>685306</v>
+        <v>685331</v>
       </c>
       <c r="R120" t="n">
-        <v>6616655</v>
+        <v>6616715</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13659,12 +13654,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13673,7 +13668,6 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -13692,10 +13686,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>114868347</v>
+        <v>114856949</v>
       </c>
       <c r="B121" t="n">
-        <v>90929</v>
+        <v>90902</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13704,42 +13698,52 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>3298</v>
+        <v>898</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>685300</v>
+        <v>685306</v>
       </c>
       <c r="R121" t="n">
-        <v>6616683</v>
+        <v>6616655</v>
       </c>
       <c r="S121" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13766,27 +13770,18 @@
           <t>2024-02-25</t>
         </is>
       </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>10:07</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2024-02-25</t>
         </is>
       </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>10:07</t>
-        </is>
-      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -13805,10 +13800,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>114885708</v>
+        <v>114868347</v>
       </c>
       <c r="B122" t="n">
-        <v>74534</v>
+        <v>90929</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13821,21 +13816,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6426</v>
+        <v>3298</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13846,13 +13841,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>685332</v>
+        <v>685300</v>
       </c>
       <c r="R122" t="n">
-        <v>6616647</v>
+        <v>6616683</v>
       </c>
       <c r="S122" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13876,12 +13871,22 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2024-02-26</t>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2024-02-26</t>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13908,10 +13913,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>114999533</v>
+        <v>114885708</v>
       </c>
       <c r="B123" t="n">
-        <v>94182</v>
+        <v>74534</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13924,33 +13929,24 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>210</v>
+        <v>6426</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
@@ -13958,13 +13954,13 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>685333</v>
+        <v>685332</v>
       </c>
       <c r="R123" t="n">
-        <v>6616685</v>
+        <v>6616647</v>
       </c>
       <c r="S123" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13988,12 +13984,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2024-02-26</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14020,10 +14016,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>114999680</v>
+        <v>114999533</v>
       </c>
       <c r="B124" t="n">
-        <v>74608</v>
+        <v>94182</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14032,44 +14028,51 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>308</v>
+        <v>210</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Barrnaturskog nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>685335</v>
+        <v>685333</v>
       </c>
       <c r="R124" t="n">
-        <v>6616662</v>
+        <v>6616685</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -14101,18 +14104,12 @@
           <t>2024-03-04</t>
         </is>
       </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>På undersidan av granlåga.</t>
-        </is>
-      </c>
       <c r="AD124" t="b">
         <v>0</v>
       </c>
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -14131,10 +14128,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>115031352</v>
+        <v>114999680</v>
       </c>
       <c r="B125" t="n">
-        <v>96514</v>
+        <v>74608</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14143,37 +14140,44 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>221944</v>
+        <v>308</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr"/>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
       <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>685317</v>
+        <v>685335</v>
       </c>
       <c r="R125" t="n">
-        <v>6616684</v>
+        <v>6616662</v>
       </c>
       <c r="S125" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14197,12 +14201,17 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2024-03-06</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2024-03-06</t>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>På undersidan av granlåga.</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14211,6 +14220,7 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -14229,10 +14239,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>115031254</v>
+        <v>115031352</v>
       </c>
       <c r="B126" t="n">
-        <v>74611</v>
+        <v>96514</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14241,41 +14251,37 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>308</v>
+        <v>221944</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Gransumpskog nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>685365</v>
+        <v>685317</v>
       </c>
       <c r="R126" t="n">
-        <v>6616656</v>
+        <v>6616684</v>
       </c>
       <c r="S126" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -14328,6 +14334,108 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>115031254</v>
+      </c>
+      <c r="B127" t="n">
+        <v>74611</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>308</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Gransumpskog nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>685365</v>
+      </c>
+      <c r="R127" t="n">
+        <v>6616656</v>
+      </c>
+      <c r="S127" t="n">
+        <v>10</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY127"/>
+  <dimension ref="A1:AY129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4119,10 +4119,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>111866680</v>
+        <v>115046071</v>
       </c>
       <c r="B32" t="n">
-        <v>89557</v>
+        <v>90281</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4153,12 +4153,9 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Upl</t>
+          <t>Gransumpskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
@@ -4168,7 +4165,7 @@
         <v>6616656</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4192,12 +4189,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-09-03</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-09-03</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4206,7 +4203,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -14437,6 +14433,210 @@
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>115046040</v>
+      </c>
+      <c r="B128" t="n">
+        <v>90263</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Gransumpskog nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>685365</v>
+      </c>
+      <c r="R128" t="n">
+        <v>6616656</v>
+      </c>
+      <c r="S128" t="n">
+        <v>10</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>115046432</v>
+      </c>
+      <c r="B129" t="n">
+        <v>90281</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Gransumpskog nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>685381</v>
+      </c>
+      <c r="R129" t="n">
+        <v>6616657</v>
+      </c>
+      <c r="S129" t="n">
+        <v>10</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY129"/>
+  <dimension ref="A1:AY130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14637,6 +14637,112 @@
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>115137366</v>
+      </c>
+      <c r="B130" t="n">
+        <v>74611</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>308</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Gransumpskog sydost om Kårsta, Upl</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>685395</v>
+      </c>
+      <c r="R130" t="n">
+        <v>6616766</v>
+      </c>
+      <c r="S130" t="n">
+        <v>10</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2024-03-12</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>2024-03-12</t>
+        </is>
+      </c>
+      <c r="AD130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF130" t="inlineStr"/>
+      <c r="AG130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -15058,7 +15058,7 @@
         <v>118717859</v>
       </c>
       <c r="B134" t="n">
-        <v>98593</v>
+        <v>98600</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY134"/>
+  <dimension ref="A1:AY142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15169,6 +15169,944 @@
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>120061691</v>
+      </c>
+      <c r="B135" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>685447</v>
+      </c>
+      <c r="R135" t="n">
+        <v>6616746</v>
+      </c>
+      <c r="S135" t="n">
+        <v>10</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>120061391</v>
+      </c>
+      <c r="B136" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>685384</v>
+      </c>
+      <c r="R136" t="n">
+        <v>6616661</v>
+      </c>
+      <c r="S136" t="n">
+        <v>10</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT136" t="inlineStr"/>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>120062150</v>
+      </c>
+      <c r="B137" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>685379</v>
+      </c>
+      <c r="R137" t="n">
+        <v>6616654</v>
+      </c>
+      <c r="S137" t="n">
+        <v>10</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>2 blomställningar</t>
+        </is>
+      </c>
+      <c r="AD137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT137" t="inlineStr"/>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>120061814</v>
+      </c>
+      <c r="B138" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Gransumpskog sydost om Kårsta, Gransumpskog sydost om Kårsta, Upl</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>685421</v>
+      </c>
+      <c r="R138" t="n">
+        <v>6616765</v>
+      </c>
+      <c r="S138" t="n">
+        <v>10</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT138" t="inlineStr"/>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>120061670</v>
+      </c>
+      <c r="B139" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>685428</v>
+      </c>
+      <c r="R139" t="n">
+        <v>6616738</v>
+      </c>
+      <c r="S139" t="n">
+        <v>10</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT139" t="inlineStr"/>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>120061280</v>
+      </c>
+      <c r="B140" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>685380</v>
+      </c>
+      <c r="R140" t="n">
+        <v>6616654</v>
+      </c>
+      <c r="S140" t="n">
+        <v>10</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>120061796</v>
+      </c>
+      <c r="B141" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>685429</v>
+      </c>
+      <c r="R141" t="n">
+        <v>6616759</v>
+      </c>
+      <c r="S141" t="n">
+        <v>10</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>En blomställning</t>
+        </is>
+      </c>
+      <c r="AD141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT141" t="inlineStr"/>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>120061896</v>
+      </c>
+      <c r="B142" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>685406</v>
+      </c>
+      <c r="R142" t="n">
+        <v>6616750</v>
+      </c>
+      <c r="S142" t="n">
+        <v>10</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -15287,7 +15287,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120061391</v>
+        <v>120062150</v>
       </c>
       <c r="B136" t="n">
         <v>97907</v>
@@ -15322,7 +15322,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -15332,7 +15332,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
@@ -15341,10 +15341,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>685384</v>
+        <v>685379</v>
       </c>
       <c r="R136" t="n">
-        <v>6616661</v>
+        <v>6616654</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15377,6 +15377,11 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15403,7 +15408,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120062150</v>
+        <v>120061391</v>
       </c>
       <c r="B137" t="n">
         <v>97907</v>
@@ -15438,7 +15443,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -15448,7 +15453,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
@@ -15457,10 +15462,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>685379</v>
+        <v>685384</v>
       </c>
       <c r="R137" t="n">
-        <v>6616654</v>
+        <v>6616661</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15493,11 +15498,6 @@
       <c r="AA137" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD137" t="b">

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -15171,7 +15171,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120061691</v>
+        <v>120061391</v>
       </c>
       <c r="B135" t="n">
         <v>97907</v>
@@ -15206,7 +15206,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -15221,14 +15221,14 @@
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>685447</v>
+        <v>685384</v>
       </c>
       <c r="R135" t="n">
-        <v>6616746</v>
+        <v>6616661</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15287,7 +15287,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120062150</v>
+        <v>120061814</v>
       </c>
       <c r="B136" t="n">
         <v>97907</v>
@@ -15322,7 +15322,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -15332,19 +15332,19 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
+          <t>Gransumpskog sydost om Kårsta, Gransumpskog sydost om Kårsta, Upl</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>685379</v>
+        <v>685421</v>
       </c>
       <c r="R136" t="n">
-        <v>6616654</v>
+        <v>6616765</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15377,11 +15377,6 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15408,7 +15403,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120061391</v>
+        <v>120061796</v>
       </c>
       <c r="B137" t="n">
         <v>97907</v>
@@ -15443,7 +15438,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -15453,19 +15448,19 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>685384</v>
+        <v>685429</v>
       </c>
       <c r="R137" t="n">
-        <v>6616661</v>
+        <v>6616759</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15498,6 +15493,11 @@
       <c r="AA137" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>En blomställning</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15524,7 +15524,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>120061814</v>
+        <v>120061280</v>
       </c>
       <c r="B138" t="n">
         <v>97907</v>
@@ -15559,7 +15559,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -15574,14 +15574,14 @@
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Gransumpskog sydost om Kårsta, Gransumpskog sydost om Kårsta, Upl</t>
+          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>685421</v>
+        <v>685380</v>
       </c>
       <c r="R138" t="n">
-        <v>6616765</v>
+        <v>6616654</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15756,7 +15756,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>120061280</v>
+        <v>120061691</v>
       </c>
       <c r="B140" t="n">
         <v>97907</v>
@@ -15791,7 +15791,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -15806,14 +15806,14 @@
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>685380</v>
+        <v>685447</v>
       </c>
       <c r="R140" t="n">
-        <v>6616654</v>
+        <v>6616746</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15872,7 +15872,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>120061796</v>
+        <v>120062150</v>
       </c>
       <c r="B141" t="n">
         <v>97907</v>
@@ -15907,7 +15907,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -15922,14 +15922,14 @@
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>685429</v>
+        <v>685379</v>
       </c>
       <c r="R141" t="n">
-        <v>6616759</v>
+        <v>6616654</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15966,7 +15966,7 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>En blomställning</t>
+          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD141" t="b">

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -15171,7 +15171,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120061391</v>
+        <v>120061796</v>
       </c>
       <c r="B135" t="n">
         <v>97907</v>
@@ -15206,7 +15206,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -15216,19 +15216,19 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>685384</v>
+        <v>685429</v>
       </c>
       <c r="R135" t="n">
-        <v>6616661</v>
+        <v>6616759</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15261,6 +15261,11 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>En blomställning</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15287,7 +15292,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120061814</v>
+        <v>120061280</v>
       </c>
       <c r="B136" t="n">
         <v>97907</v>
@@ -15322,7 +15327,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -15337,14 +15342,14 @@
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Gransumpskog sydost om Kårsta, Gransumpskog sydost om Kårsta, Upl</t>
+          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>685421</v>
+        <v>685380</v>
       </c>
       <c r="R136" t="n">
-        <v>6616765</v>
+        <v>6616654</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15403,7 +15408,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120061796</v>
+        <v>120061670</v>
       </c>
       <c r="B137" t="n">
         <v>97907</v>
@@ -15438,7 +15443,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -15448,7 +15453,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
@@ -15457,10 +15462,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>685429</v>
+        <v>685428</v>
       </c>
       <c r="R137" t="n">
-        <v>6616759</v>
+        <v>6616738</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15493,11 +15498,6 @@
       <c r="AA137" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>En blomställning</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15524,7 +15524,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>120061280</v>
+        <v>120061814</v>
       </c>
       <c r="B138" t="n">
         <v>97907</v>
@@ -15559,7 +15559,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -15574,14 +15574,14 @@
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
+          <t>Gransumpskog sydost om Kårsta, Gransumpskog sydost om Kårsta, Upl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>685380</v>
+        <v>685421</v>
       </c>
       <c r="R138" t="n">
-        <v>6616654</v>
+        <v>6616765</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15640,7 +15640,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>120061670</v>
+        <v>120061896</v>
       </c>
       <c r="B139" t="n">
         <v>97907</v>
@@ -15675,7 +15675,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>71</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -15694,10 +15694,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>685428</v>
+        <v>685406</v>
       </c>
       <c r="R139" t="n">
-        <v>6616738</v>
+        <v>6616750</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15756,7 +15756,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>120061691</v>
+        <v>120062150</v>
       </c>
       <c r="B140" t="n">
         <v>97907</v>
@@ -15791,7 +15791,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -15801,19 +15801,19 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>685447</v>
+        <v>685379</v>
       </c>
       <c r="R140" t="n">
-        <v>6616746</v>
+        <v>6616654</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15846,6 +15846,11 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15872,7 +15877,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>120062150</v>
+        <v>120061391</v>
       </c>
       <c r="B141" t="n">
         <v>97907</v>
@@ -15907,7 +15912,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -15917,7 +15922,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -15926,10 +15931,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>685379</v>
+        <v>685384</v>
       </c>
       <c r="R141" t="n">
-        <v>6616654</v>
+        <v>6616661</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15962,11 +15967,6 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15993,7 +15993,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>120061896</v>
+        <v>120061691</v>
       </c>
       <c r="B142" t="n">
         <v>97907</v>
@@ -16028,7 +16028,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -16047,10 +16047,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>685406</v>
+        <v>685447</v>
       </c>
       <c r="R142" t="n">
-        <v>6616750</v>
+        <v>6616746</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -15171,7 +15171,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120061796</v>
+        <v>120062150</v>
       </c>
       <c r="B135" t="n">
         <v>97907</v>
@@ -15206,7 +15206,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -15221,14 +15221,14 @@
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>685429</v>
+        <v>685379</v>
       </c>
       <c r="R135" t="n">
-        <v>6616759</v>
+        <v>6616654</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15265,7 +15265,7 @@
       </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>En blomställning</t>
+          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15640,7 +15640,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>120061896</v>
+        <v>120061796</v>
       </c>
       <c r="B139" t="n">
         <v>97907</v>
@@ -15675,7 +15675,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -15685,7 +15685,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
@@ -15694,10 +15694,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>685406</v>
+        <v>685429</v>
       </c>
       <c r="R139" t="n">
-        <v>6616750</v>
+        <v>6616759</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15730,6 +15730,11 @@
       <c r="AA139" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>En blomställning</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15756,7 +15761,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>120062150</v>
+        <v>120061691</v>
       </c>
       <c r="B140" t="n">
         <v>97907</v>
@@ -15791,7 +15796,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -15801,19 +15806,19 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>685379</v>
+        <v>685447</v>
       </c>
       <c r="R140" t="n">
-        <v>6616654</v>
+        <v>6616746</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15846,11 +15851,6 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15877,7 +15877,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>120061391</v>
+        <v>120061896</v>
       </c>
       <c r="B141" t="n">
         <v>97907</v>
@@ -15912,7 +15912,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>71</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -15927,14 +15927,14 @@
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>685384</v>
+        <v>685406</v>
       </c>
       <c r="R141" t="n">
-        <v>6616661</v>
+        <v>6616750</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15993,7 +15993,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>120061691</v>
+        <v>120061391</v>
       </c>
       <c r="B142" t="n">
         <v>97907</v>
@@ -16028,7 +16028,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -16043,14 +16043,14 @@
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>685447</v>
+        <v>685384</v>
       </c>
       <c r="R142" t="n">
-        <v>6616746</v>
+        <v>6616661</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -15171,10 +15171,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120062150</v>
+        <v>120061896</v>
       </c>
       <c r="B135" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>71</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -15216,19 +15216,19 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>685379</v>
+        <v>685406</v>
       </c>
       <c r="R135" t="n">
-        <v>6616654</v>
+        <v>6616750</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15261,11 +15261,6 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15295,7 +15290,7 @@
         <v>120061280</v>
       </c>
       <c r="B136" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15408,10 +15403,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120061670</v>
+        <v>120061814</v>
       </c>
       <c r="B137" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15443,7 +15438,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -15458,14 +15453,14 @@
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Gransumpskog sydost om Kårsta, Gransumpskog sydost om Kårsta, Upl</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>685428</v>
+        <v>685421</v>
       </c>
       <c r="R137" t="n">
-        <v>6616738</v>
+        <v>6616765</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15524,10 +15519,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>120061814</v>
+        <v>120061691</v>
       </c>
       <c r="B138" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15559,7 +15554,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -15574,14 +15569,14 @@
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Gransumpskog sydost om Kårsta, Gransumpskog sydost om Kårsta, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>685421</v>
+        <v>685447</v>
       </c>
       <c r="R138" t="n">
-        <v>6616765</v>
+        <v>6616746</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15640,10 +15635,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>120061796</v>
+        <v>120061391</v>
       </c>
       <c r="B139" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15675,7 +15670,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -15685,19 +15680,19 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>685429</v>
+        <v>685384</v>
       </c>
       <c r="R139" t="n">
-        <v>6616759</v>
+        <v>6616661</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15730,11 +15725,6 @@
       <c r="AA139" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>En blomställning</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15761,10 +15751,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>120061691</v>
+        <v>120061670</v>
       </c>
       <c r="B140" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15796,7 +15786,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -15815,10 +15805,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>685447</v>
+        <v>685428</v>
       </c>
       <c r="R140" t="n">
-        <v>6616746</v>
+        <v>6616738</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15877,10 +15867,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>120061896</v>
+        <v>120062150</v>
       </c>
       <c r="B141" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15912,7 +15902,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -15922,19 +15912,19 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>685406</v>
+        <v>685379</v>
       </c>
       <c r="R141" t="n">
-        <v>6616750</v>
+        <v>6616654</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15967,6 +15957,11 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15993,10 +15988,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>120061391</v>
+        <v>120061796</v>
       </c>
       <c r="B142" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -16028,7 +16023,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -16038,19 +16033,19 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>685384</v>
+        <v>685429</v>
       </c>
       <c r="R142" t="n">
-        <v>6616661</v>
+        <v>6616759</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16083,6 +16078,11 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>En blomställning</t>
         </is>
       </c>
       <c r="AD142" t="b">

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY142"/>
+  <dimension ref="A1:AY143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15171,7 +15171,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120061896</v>
+        <v>120061391</v>
       </c>
       <c r="B135" t="n">
         <v>97930</v>
@@ -15206,7 +15206,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -15221,14 +15221,14 @@
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>685406</v>
+        <v>685384</v>
       </c>
       <c r="R135" t="n">
-        <v>6616750</v>
+        <v>6616661</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15287,7 +15287,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120061280</v>
+        <v>120061896</v>
       </c>
       <c r="B136" t="n">
         <v>97930</v>
@@ -15322,7 +15322,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>71</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -15337,14 +15337,14 @@
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>685380</v>
+        <v>685406</v>
       </c>
       <c r="R136" t="n">
-        <v>6616654</v>
+        <v>6616750</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15403,7 +15403,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120061814</v>
+        <v>120061670</v>
       </c>
       <c r="B137" t="n">
         <v>97930</v>
@@ -15438,7 +15438,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -15453,14 +15453,14 @@
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Gransumpskog sydost om Kårsta, Gransumpskog sydost om Kårsta, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>685421</v>
+        <v>685428</v>
       </c>
       <c r="R137" t="n">
-        <v>6616765</v>
+        <v>6616738</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15519,7 +15519,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>120061691</v>
+        <v>120061814</v>
       </c>
       <c r="B138" t="n">
         <v>97930</v>
@@ -15554,7 +15554,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -15569,14 +15569,14 @@
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Gransumpskog sydost om Kårsta, Gransumpskog sydost om Kårsta, Upl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>685447</v>
+        <v>685421</v>
       </c>
       <c r="R138" t="n">
-        <v>6616746</v>
+        <v>6616765</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15635,7 +15635,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>120061391</v>
+        <v>120061796</v>
       </c>
       <c r="B139" t="n">
         <v>97930</v>
@@ -15670,7 +15670,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -15680,19 +15680,19 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>685384</v>
+        <v>685429</v>
       </c>
       <c r="R139" t="n">
-        <v>6616661</v>
+        <v>6616759</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15725,6 +15725,11 @@
       <c r="AA139" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>En blomställning</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15751,7 +15756,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>120061670</v>
+        <v>120062150</v>
       </c>
       <c r="B140" t="n">
         <v>97930</v>
@@ -15786,7 +15791,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -15796,19 +15801,19 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>685428</v>
+        <v>685379</v>
       </c>
       <c r="R140" t="n">
-        <v>6616738</v>
+        <v>6616654</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15841,6 +15846,11 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15867,7 +15877,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>120062150</v>
+        <v>120061691</v>
       </c>
       <c r="B141" t="n">
         <v>97930</v>
@@ -15902,7 +15912,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -15912,19 +15922,19 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>685379</v>
+        <v>685447</v>
       </c>
       <c r="R141" t="n">
-        <v>6616654</v>
+        <v>6616746</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15957,11 +15967,6 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15988,7 +15993,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>120061796</v>
+        <v>120061280</v>
       </c>
       <c r="B142" t="n">
         <v>97930</v>
@@ -16023,7 +16028,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -16033,19 +16038,19 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>685429</v>
+        <v>685380</v>
       </c>
       <c r="R142" t="n">
-        <v>6616759</v>
+        <v>6616654</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16080,11 +16085,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>En blomställning</t>
-        </is>
-      </c>
       <c r="AD142" t="b">
         <v>0</v>
       </c>
@@ -16106,6 +16106,112 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>119812067</v>
+      </c>
+      <c r="B143" t="n">
+        <v>90092</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>5741</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Tjockfotad fingersvamp</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Ramaria flavescens</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Barrnaturskog nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>685340</v>
+      </c>
+      <c r="R143" t="n">
+        <v>6616746</v>
+      </c>
+      <c r="S143" t="n">
+        <v>10</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AD143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF143" t="inlineStr"/>
+      <c r="AG143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -15287,7 +15287,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120061896</v>
+        <v>120061691</v>
       </c>
       <c r="B136" t="n">
         <v>97930</v>
@@ -15322,7 +15322,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -15341,10 +15341,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>685406</v>
+        <v>685447</v>
       </c>
       <c r="R136" t="n">
-        <v>6616750</v>
+        <v>6616746</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15403,7 +15403,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120061670</v>
+        <v>120061280</v>
       </c>
       <c r="B137" t="n">
         <v>97930</v>
@@ -15438,7 +15438,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -15453,14 +15453,14 @@
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>685428</v>
+        <v>685380</v>
       </c>
       <c r="R137" t="n">
-        <v>6616738</v>
+        <v>6616654</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15519,7 +15519,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>120061814</v>
+        <v>120061796</v>
       </c>
       <c r="B138" t="n">
         <v>97930</v>
@@ -15554,7 +15554,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -15564,19 +15564,19 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Gransumpskog sydost om Kårsta, Gransumpskog sydost om Kårsta, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>685421</v>
+        <v>685429</v>
       </c>
       <c r="R138" t="n">
-        <v>6616765</v>
+        <v>6616759</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15609,6 +15609,11 @@
       <c r="AA138" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>En blomställning</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15635,7 +15640,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>120061796</v>
+        <v>120061670</v>
       </c>
       <c r="B139" t="n">
         <v>97930</v>
@@ -15670,7 +15675,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -15680,7 +15685,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
@@ -15689,10 +15694,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>685429</v>
+        <v>685428</v>
       </c>
       <c r="R139" t="n">
-        <v>6616759</v>
+        <v>6616738</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15725,11 +15730,6 @@
       <c r="AA139" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>En blomställning</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15877,7 +15877,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>120061691</v>
+        <v>120061814</v>
       </c>
       <c r="B141" t="n">
         <v>97930</v>
@@ -15912,7 +15912,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -15927,14 +15927,14 @@
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Gransumpskog sydost om Kårsta, Gransumpskog sydost om Kårsta, Upl</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>685447</v>
+        <v>685421</v>
       </c>
       <c r="R141" t="n">
-        <v>6616746</v>
+        <v>6616765</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15993,7 +15993,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>120061280</v>
+        <v>120061896</v>
       </c>
       <c r="B142" t="n">
         <v>97930</v>
@@ -16028,7 +16028,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>71</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -16043,14 +16043,14 @@
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>685380</v>
+        <v>685406</v>
       </c>
       <c r="R142" t="n">
-        <v>6616654</v>
+        <v>6616750</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -15171,7 +15171,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120061391</v>
+        <v>120061796</v>
       </c>
       <c r="B135" t="n">
         <v>97930</v>
@@ -15206,7 +15206,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -15216,19 +15216,19 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>685384</v>
+        <v>685429</v>
       </c>
       <c r="R135" t="n">
-        <v>6616661</v>
+        <v>6616759</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15261,6 +15261,11 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>En blomställning</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15287,7 +15292,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120061691</v>
+        <v>120062150</v>
       </c>
       <c r="B136" t="n">
         <v>97930</v>
@@ -15322,7 +15327,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -15332,19 +15337,19 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>685447</v>
+        <v>685379</v>
       </c>
       <c r="R136" t="n">
-        <v>6616746</v>
+        <v>6616654</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15377,6 +15382,11 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15403,7 +15413,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120061280</v>
+        <v>120061691</v>
       </c>
       <c r="B137" t="n">
         <v>97930</v>
@@ -15438,7 +15448,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -15453,14 +15463,14 @@
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>685380</v>
+        <v>685447</v>
       </c>
       <c r="R137" t="n">
-        <v>6616654</v>
+        <v>6616746</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15519,7 +15529,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>120061796</v>
+        <v>120061896</v>
       </c>
       <c r="B138" t="n">
         <v>97930</v>
@@ -15554,7 +15564,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>71</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -15564,7 +15574,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
@@ -15573,10 +15583,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>685429</v>
+        <v>685406</v>
       </c>
       <c r="R138" t="n">
-        <v>6616759</v>
+        <v>6616750</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15609,11 +15619,6 @@
       <c r="AA138" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>En blomställning</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15756,7 +15761,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>120062150</v>
+        <v>120061280</v>
       </c>
       <c r="B140" t="n">
         <v>97930</v>
@@ -15791,7 +15796,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -15801,7 +15806,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
@@ -15810,7 +15815,7 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>685379</v>
+        <v>685380</v>
       </c>
       <c r="R140" t="n">
         <v>6616654</v>
@@ -15846,11 +15851,6 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15993,7 +15993,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>120061896</v>
+        <v>120061391</v>
       </c>
       <c r="B142" t="n">
         <v>97930</v>
@@ -16028,7 +16028,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -16043,14 +16043,14 @@
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>685406</v>
+        <v>685384</v>
       </c>
       <c r="R142" t="n">
-        <v>6616750</v>
+        <v>6616661</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -15171,7 +15171,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120061796</v>
+        <v>120061391</v>
       </c>
       <c r="B135" t="n">
         <v>97930</v>
@@ -15206,7 +15206,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -15216,19 +15216,19 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>685429</v>
+        <v>685384</v>
       </c>
       <c r="R135" t="n">
-        <v>6616759</v>
+        <v>6616661</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15261,11 +15261,6 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>En blomställning</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15292,7 +15287,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120062150</v>
+        <v>120061896</v>
       </c>
       <c r="B136" t="n">
         <v>97930</v>
@@ -15327,7 +15322,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>71</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -15337,19 +15332,19 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>685379</v>
+        <v>685406</v>
       </c>
       <c r="R136" t="n">
-        <v>6616654</v>
+        <v>6616750</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15382,11 +15377,6 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15413,7 +15403,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120061691</v>
+        <v>120061814</v>
       </c>
       <c r="B137" t="n">
         <v>97930</v>
@@ -15448,7 +15438,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -15463,14 +15453,14 @@
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Gransumpskog sydost om Kårsta, Gransumpskog sydost om Kårsta, Upl</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>685447</v>
+        <v>685421</v>
       </c>
       <c r="R137" t="n">
-        <v>6616746</v>
+        <v>6616765</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15529,7 +15519,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>120061896</v>
+        <v>120061670</v>
       </c>
       <c r="B138" t="n">
         <v>97930</v>
@@ -15564,7 +15554,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -15583,10 +15573,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>685406</v>
+        <v>685428</v>
       </c>
       <c r="R138" t="n">
-        <v>6616750</v>
+        <v>6616738</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15645,7 +15635,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>120061670</v>
+        <v>120062150</v>
       </c>
       <c r="B139" t="n">
         <v>97930</v>
@@ -15680,7 +15670,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -15690,19 +15680,19 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>685428</v>
+        <v>685379</v>
       </c>
       <c r="R139" t="n">
-        <v>6616738</v>
+        <v>6616654</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15735,6 +15725,11 @@
       <c r="AA139" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15877,7 +15872,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>120061814</v>
+        <v>120061796</v>
       </c>
       <c r="B141" t="n">
         <v>97930</v>
@@ -15912,7 +15907,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -15922,19 +15917,19 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Gransumpskog sydost om Kårsta, Gransumpskog sydost om Kårsta, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>685421</v>
+        <v>685429</v>
       </c>
       <c r="R141" t="n">
-        <v>6616765</v>
+        <v>6616759</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15967,6 +15962,11 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>En blomställning</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15993,7 +15993,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>120061391</v>
+        <v>120061691</v>
       </c>
       <c r="B142" t="n">
         <v>97930</v>
@@ -16028,7 +16028,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -16043,14 +16043,14 @@
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>685384</v>
+        <v>685447</v>
       </c>
       <c r="R142" t="n">
-        <v>6616661</v>
+        <v>6616746</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -15171,7 +15171,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120061391</v>
+        <v>120061670</v>
       </c>
       <c r="B135" t="n">
         <v>97930</v>
@@ -15206,7 +15206,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -15221,14 +15221,14 @@
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>685384</v>
+        <v>685428</v>
       </c>
       <c r="R135" t="n">
-        <v>6616661</v>
+        <v>6616738</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15287,7 +15287,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120061896</v>
+        <v>120061280</v>
       </c>
       <c r="B136" t="n">
         <v>97930</v>
@@ -15322,7 +15322,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -15337,14 +15337,14 @@
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>685406</v>
+        <v>685380</v>
       </c>
       <c r="R136" t="n">
-        <v>6616750</v>
+        <v>6616654</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15519,7 +15519,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>120061670</v>
+        <v>120061796</v>
       </c>
       <c r="B138" t="n">
         <v>97930</v>
@@ -15554,7 +15554,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -15564,7 +15564,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
@@ -15573,10 +15573,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>685428</v>
+        <v>685429</v>
       </c>
       <c r="R138" t="n">
-        <v>6616738</v>
+        <v>6616759</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15609,6 +15609,11 @@
       <c r="AA138" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>En blomställning</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15635,7 +15640,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>120062150</v>
+        <v>120061691</v>
       </c>
       <c r="B139" t="n">
         <v>97930</v>
@@ -15670,7 +15675,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -15680,19 +15685,19 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>685379</v>
+        <v>685447</v>
       </c>
       <c r="R139" t="n">
-        <v>6616654</v>
+        <v>6616746</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15725,11 +15730,6 @@
       <c r="AA139" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15756,7 +15756,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>120061280</v>
+        <v>120061896</v>
       </c>
       <c r="B140" t="n">
         <v>97930</v>
@@ -15791,7 +15791,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>71</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -15806,14 +15806,14 @@
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>685380</v>
+        <v>685406</v>
       </c>
       <c r="R140" t="n">
-        <v>6616654</v>
+        <v>6616750</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15872,7 +15872,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>120061796</v>
+        <v>120062150</v>
       </c>
       <c r="B141" t="n">
         <v>97930</v>
@@ -15907,7 +15907,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -15922,14 +15922,14 @@
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>685429</v>
+        <v>685379</v>
       </c>
       <c r="R141" t="n">
-        <v>6616759</v>
+        <v>6616654</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15966,7 +15966,7 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>En blomställning</t>
+          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15993,7 +15993,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>120061691</v>
+        <v>120061391</v>
       </c>
       <c r="B142" t="n">
         <v>97930</v>
@@ -16028,7 +16028,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -16043,14 +16043,14 @@
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>685447</v>
+        <v>685384</v>
       </c>
       <c r="R142" t="n">
-        <v>6616746</v>
+        <v>6616661</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -15171,7 +15171,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120061670</v>
+        <v>120061796</v>
       </c>
       <c r="B135" t="n">
         <v>97930</v>
@@ -15206,7 +15206,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -15216,7 +15216,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -15225,10 +15225,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>685428</v>
+        <v>685429</v>
       </c>
       <c r="R135" t="n">
-        <v>6616738</v>
+        <v>6616759</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15261,6 +15261,11 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>En blomställning</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15403,7 +15408,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120061814</v>
+        <v>120061691</v>
       </c>
       <c r="B137" t="n">
         <v>97930</v>
@@ -15438,7 +15443,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -15453,14 +15458,14 @@
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Gransumpskog sydost om Kårsta, Gransumpskog sydost om Kårsta, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>685421</v>
+        <v>685447</v>
       </c>
       <c r="R137" t="n">
-        <v>6616765</v>
+        <v>6616746</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15519,7 +15524,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>120061796</v>
+        <v>120061391</v>
       </c>
       <c r="B138" t="n">
         <v>97930</v>
@@ -15554,7 +15559,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -15564,19 +15569,19 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>685429</v>
+        <v>685384</v>
       </c>
       <c r="R138" t="n">
-        <v>6616759</v>
+        <v>6616661</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15609,11 +15614,6 @@
       <c r="AA138" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>En blomställning</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15640,7 +15640,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>120061691</v>
+        <v>120061814</v>
       </c>
       <c r="B139" t="n">
         <v>97930</v>
@@ -15675,7 +15675,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -15690,14 +15690,14 @@
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Gransumpskog sydost om Kårsta, Gransumpskog sydost om Kårsta, Upl</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>685447</v>
+        <v>685421</v>
       </c>
       <c r="R139" t="n">
-        <v>6616746</v>
+        <v>6616765</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15756,7 +15756,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>120061896</v>
+        <v>120061670</v>
       </c>
       <c r="B140" t="n">
         <v>97930</v>
@@ -15791,7 +15791,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -15810,10 +15810,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>685406</v>
+        <v>685428</v>
       </c>
       <c r="R140" t="n">
-        <v>6616750</v>
+        <v>6616738</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15993,7 +15993,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>120061391</v>
+        <v>120061896</v>
       </c>
       <c r="B142" t="n">
         <v>97930</v>
@@ -16028,7 +16028,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>71</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -16043,14 +16043,14 @@
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>685384</v>
+        <v>685406</v>
       </c>
       <c r="R142" t="n">
-        <v>6616661</v>
+        <v>6616750</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -18337,7 +18337,7 @@
         <v>120836325</v>
       </c>
       <c r="B162" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>121343884</v>
       </c>
       <c r="B163" t="n">
-        <v>97017</v>
+        <v>97027</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -18337,7 +18337,7 @@
         <v>120836325</v>
       </c>
       <c r="B162" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>121343884</v>
       </c>
       <c r="B163" t="n">
-        <v>97027</v>
+        <v>97040</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -18337,7 +18337,7 @@
         <v>120836325</v>
       </c>
       <c r="B162" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>121343884</v>
       </c>
       <c r="B163" t="n">
-        <v>97040</v>
+        <v>97041</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -18337,7 +18337,7 @@
         <v>120836325</v>
       </c>
       <c r="B162" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>121343884</v>
       </c>
       <c r="B163" t="n">
-        <v>97041</v>
+        <v>97044</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY163"/>
+  <dimension ref="A1:AY164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18453,7 +18453,7 @@
         <v>121343884</v>
       </c>
       <c r="B163" t="n">
-        <v>97044</v>
+        <v>97050</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -18549,6 +18549,113 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>121567592</v>
+      </c>
+      <c r="B164" t="n">
+        <v>8435</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q164" t="n">
+        <v>685437</v>
+      </c>
+      <c r="R164" t="n">
+        <v>6616649</v>
+      </c>
+      <c r="S164" t="n">
+        <v>10</v>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W164" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>2024-12-12</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>2024-12-12</t>
+        </is>
+      </c>
+      <c r="AD164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT164" t="inlineStr"/>
+      <c r="AW164" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX164" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -18453,7 +18453,7 @@
         <v>121343884</v>
       </c>
       <c r="B163" t="n">
-        <v>97050</v>
+        <v>97051</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -18453,7 +18453,7 @@
         <v>121343884</v>
       </c>
       <c r="B163" t="n">
-        <v>97051</v>
+        <v>97059</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -18555,7 +18555,7 @@
         <v>121567592</v>
       </c>
       <c r="B164" t="n">
-        <v>8435</v>
+        <v>8436</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -18787,7 +18787,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121735531</v>
+        <v>121734849</v>
       </c>
       <c r="B166" t="n">
         <v>98113</v>
@@ -18822,7 +18822,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -18841,10 +18841,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>685357</v>
+        <v>685480</v>
       </c>
       <c r="R166" t="n">
-        <v>6616798</v>
+        <v>6616744</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18903,7 +18903,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121735377</v>
+        <v>121734727</v>
       </c>
       <c r="B167" t="n">
         <v>98113</v>
@@ -18938,7 +18938,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -18951,16 +18951,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>685440</v>
+        <v>685481</v>
       </c>
       <c r="R167" t="n">
-        <v>6616805</v>
+        <v>6616734</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19001,6 +19003,7 @@
       <c r="AE167" t="b">
         <v>0</v>
       </c>
+      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
@@ -19019,7 +19022,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121735485</v>
+        <v>121735531</v>
       </c>
       <c r="B168" t="n">
         <v>98113</v>
@@ -19054,7 +19057,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -19064,21 +19067,19 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L168" t="inlineStr"/>
-      <c r="N168" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P168" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>685409</v>
+        <v>685357</v>
       </c>
       <c r="R168" t="n">
-        <v>6616795</v>
+        <v>6616798</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19113,18 +19114,12 @@
           <t>2024-12-25</t>
         </is>
       </c>
-      <c r="AC168" t="inlineStr">
-        <is>
-          <t>4 blomställningar</t>
-        </is>
-      </c>
       <c r="AD168" t="b">
         <v>0</v>
       </c>
       <c r="AE168" t="b">
         <v>0</v>
       </c>
-      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
@@ -19143,7 +19138,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>121734727</v>
+        <v>121734887</v>
       </c>
       <c r="B169" t="n">
         <v>98113</v>
@@ -19178,7 +19173,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -19191,18 +19186,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>685481</v>
+        <v>685475</v>
       </c>
       <c r="R169" t="n">
-        <v>6616734</v>
+        <v>6616757</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19243,7 +19236,6 @@
       <c r="AE169" t="b">
         <v>0</v>
       </c>
-      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
@@ -19262,7 +19254,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>121734887</v>
+        <v>121735416</v>
       </c>
       <c r="B170" t="n">
         <v>98113</v>
@@ -19297,7 +19289,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -19316,10 +19308,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>685475</v>
+        <v>685413</v>
       </c>
       <c r="R170" t="n">
-        <v>6616757</v>
+        <v>6616793</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19378,10 +19370,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>121733071</v>
+        <v>121735377</v>
       </c>
       <c r="B171" t="n">
-        <v>90748</v>
+        <v>98113</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -19390,38 +19382,52 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>685246</v>
+        <v>685440</v>
       </c>
       <c r="R171" t="n">
-        <v>6616659</v>
+        <v>6616805</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19480,7 +19486,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121734849</v>
+        <v>121735485</v>
       </c>
       <c r="B172" t="n">
         <v>98113</v>
@@ -19515,7 +19521,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>78</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -19525,19 +19531,21 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>685480</v>
+        <v>685409</v>
       </c>
       <c r="R172" t="n">
-        <v>6616744</v>
+        <v>6616795</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19572,12 +19580,18 @@
           <t>2024-12-25</t>
         </is>
       </c>
+      <c r="AC172" t="inlineStr">
+        <is>
+          <t>4 blomställningar</t>
+        </is>
+      </c>
       <c r="AD172" t="b">
         <v>0</v>
       </c>
       <c r="AE172" t="b">
         <v>0</v>
       </c>
+      <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="b">
         <v>0</v>
       </c>
@@ -19596,10 +19610,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>121735416</v>
+        <v>121733071</v>
       </c>
       <c r="B173" t="n">
-        <v>98113</v>
+        <v>90748</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -19608,52 +19622,38 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>685413</v>
+        <v>685246</v>
       </c>
       <c r="R173" t="n">
-        <v>6616793</v>
+        <v>6616659</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19712,7 +19712,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>121735074</v>
+        <v>121735498</v>
       </c>
       <c r="B174" t="n">
         <v>98113</v>
@@ -19747,7 +19747,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -19766,10 +19766,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>685486</v>
+        <v>685410</v>
       </c>
       <c r="R174" t="n">
-        <v>6616781</v>
+        <v>6616808</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19828,7 +19828,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>121735498</v>
+        <v>121735074</v>
       </c>
       <c r="B175" t="n">
         <v>98113</v>
@@ -19863,7 +19863,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -19882,10 +19882,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>685410</v>
+        <v>685486</v>
       </c>
       <c r="R175" t="n">
-        <v>6616808</v>
+        <v>6616781</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19944,7 +19944,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>121743769</v>
+        <v>121735053</v>
       </c>
       <c r="B176" t="n">
         <v>98113</v>
@@ -19979,7 +19979,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>242</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -19989,7 +19989,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L176" t="inlineStr"/>
@@ -20000,10 +20000,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>685401</v>
+        <v>685473</v>
       </c>
       <c r="R176" t="n">
-        <v>6616722</v>
+        <v>6616791</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -20030,17 +20030,17 @@
       </c>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-12-25</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-12-25</t>
         </is>
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>Återbesök</t>
+          <t>En blomställning</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -20192,7 +20192,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>121735053</v>
+        <v>121743769</v>
       </c>
       <c r="B178" t="n">
         <v>98113</v>
@@ -20227,7 +20227,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -20237,7 +20237,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L178" t="inlineStr"/>
@@ -20248,10 +20248,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>685473</v>
+        <v>685401</v>
       </c>
       <c r="R178" t="n">
-        <v>6616791</v>
+        <v>6616722</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20278,17 +20278,17 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>En blomställning</t>
+          <t>Återbesök</t>
         </is>
       </c>
       <c r="AD178" t="b">

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -18787,7 +18787,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121734849</v>
+        <v>121734727</v>
       </c>
       <c r="B166" t="n">
         <v>98113</v>
@@ -18822,7 +18822,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -18835,16 +18835,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L166" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>685480</v>
+        <v>685481</v>
       </c>
       <c r="R166" t="n">
-        <v>6616744</v>
+        <v>6616734</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18885,6 +18887,7 @@
       <c r="AE166" t="b">
         <v>0</v>
       </c>
+      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
       </c>
@@ -18903,7 +18906,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121734727</v>
+        <v>121735485</v>
       </c>
       <c r="B167" t="n">
         <v>98113</v>
@@ -18938,7 +18941,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>78</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -18948,7 +18951,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L167" t="inlineStr"/>
@@ -18959,10 +18962,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>685481</v>
+        <v>685409</v>
       </c>
       <c r="R167" t="n">
-        <v>6616734</v>
+        <v>6616795</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18995,6 +18998,11 @@
       <c r="AA167" t="inlineStr">
         <is>
           <t>2024-12-25</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>4 blomställningar</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -19138,7 +19146,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>121734887</v>
+        <v>121735416</v>
       </c>
       <c r="B169" t="n">
         <v>98113</v>
@@ -19173,7 +19181,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -19192,10 +19200,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>685475</v>
+        <v>685413</v>
       </c>
       <c r="R169" t="n">
-        <v>6616757</v>
+        <v>6616793</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19254,10 +19262,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>121735416</v>
+        <v>121733071</v>
       </c>
       <c r="B170" t="n">
-        <v>98113</v>
+        <v>90748</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -19266,52 +19274,38 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J170" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>685413</v>
+        <v>685246</v>
       </c>
       <c r="R170" t="n">
-        <v>6616793</v>
+        <v>6616659</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19486,7 +19480,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121735485</v>
+        <v>121734849</v>
       </c>
       <c r="B172" t="n">
         <v>98113</v>
@@ -19521,7 +19515,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -19531,21 +19525,19 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L172" t="inlineStr"/>
-      <c r="N172" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P172" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>685409</v>
+        <v>685480</v>
       </c>
       <c r="R172" t="n">
-        <v>6616795</v>
+        <v>6616744</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19580,18 +19572,12 @@
           <t>2024-12-25</t>
         </is>
       </c>
-      <c r="AC172" t="inlineStr">
-        <is>
-          <t>4 blomställningar</t>
-        </is>
-      </c>
       <c r="AD172" t="b">
         <v>0</v>
       </c>
       <c r="AE172" t="b">
         <v>0</v>
       </c>
-      <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="b">
         <v>0</v>
       </c>
@@ -19610,10 +19596,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>121733071</v>
+        <v>121735074</v>
       </c>
       <c r="B173" t="n">
-        <v>90748</v>
+        <v>98113</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -19622,38 +19608,52 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>685246</v>
+        <v>685486</v>
       </c>
       <c r="R173" t="n">
-        <v>6616659</v>
+        <v>6616781</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19828,7 +19828,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>121735074</v>
+        <v>121734887</v>
       </c>
       <c r="B175" t="n">
         <v>98113</v>
@@ -19863,7 +19863,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -19882,10 +19882,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>685486</v>
+        <v>685475</v>
       </c>
       <c r="R175" t="n">
-        <v>6616781</v>
+        <v>6616757</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19944,7 +19944,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>121735053</v>
+        <v>121743769</v>
       </c>
       <c r="B176" t="n">
         <v>98113</v>
@@ -19979,7 +19979,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -19989,7 +19989,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L176" t="inlineStr"/>
@@ -20000,10 +20000,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>685473</v>
+        <v>685401</v>
       </c>
       <c r="R176" t="n">
-        <v>6616791</v>
+        <v>6616722</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -20030,17 +20030,17 @@
       </c>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>En blomställning</t>
+          <t>Återbesök</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -20068,7 +20068,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>121734526</v>
+        <v>121735053</v>
       </c>
       <c r="B177" t="n">
         <v>98113</v>
@@ -20103,7 +20103,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>242</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -20113,7 +20113,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L177" t="inlineStr"/>
@@ -20124,10 +20124,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>685452</v>
+        <v>685473</v>
       </c>
       <c r="R177" t="n">
-        <v>6616694</v>
+        <v>6616791</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -20164,7 +20164,7 @@
       </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>Återbesök. Kring en äldre tall.</t>
+          <t>En blomställning</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20192,7 +20192,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>121743769</v>
+        <v>121734526</v>
       </c>
       <c r="B178" t="n">
         <v>98113</v>
@@ -20227,7 +20227,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>57</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -20248,10 +20248,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>685401</v>
+        <v>685452</v>
       </c>
       <c r="R178" t="n">
-        <v>6616722</v>
+        <v>6616694</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20278,17 +20278,17 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-12-25</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-12-25</t>
         </is>
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>Återbesök</t>
+          <t>Återbesök. Kring en äldre tall.</t>
         </is>
       </c>
       <c r="AD178" t="b">

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -18668,7 +18668,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121735325</v>
+        <v>121735074</v>
       </c>
       <c r="B165" t="n">
         <v>98113</v>
@@ -18703,7 +18703,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -18716,18 +18716,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>685448</v>
+        <v>685486</v>
       </c>
       <c r="R165" t="n">
-        <v>6616789</v>
+        <v>6616781</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18768,7 +18766,6 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
-      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
@@ -18787,7 +18784,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121734727</v>
+        <v>121735498</v>
       </c>
       <c r="B166" t="n">
         <v>98113</v>
@@ -18822,7 +18819,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -18835,18 +18832,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L166" t="inlineStr"/>
-      <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>685481</v>
+        <v>685410</v>
       </c>
       <c r="R166" t="n">
-        <v>6616734</v>
+        <v>6616808</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18887,7 +18882,6 @@
       <c r="AE166" t="b">
         <v>0</v>
       </c>
-      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
       </c>
@@ -18906,7 +18900,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121735485</v>
+        <v>121735325</v>
       </c>
       <c r="B167" t="n">
         <v>98113</v>
@@ -18941,7 +18935,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -18951,7 +18945,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L167" t="inlineStr"/>
@@ -18962,10 +18956,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>685409</v>
+        <v>685448</v>
       </c>
       <c r="R167" t="n">
-        <v>6616795</v>
+        <v>6616789</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18998,11 +18992,6 @@
       <c r="AA167" t="inlineStr">
         <is>
           <t>2024-12-25</t>
-        </is>
-      </c>
-      <c r="AC167" t="inlineStr">
-        <is>
-          <t>4 blomställningar</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -19030,7 +19019,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121735531</v>
+        <v>121734849</v>
       </c>
       <c r="B168" t="n">
         <v>98113</v>
@@ -19065,7 +19054,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -19084,10 +19073,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>685357</v>
+        <v>685480</v>
       </c>
       <c r="R168" t="n">
-        <v>6616798</v>
+        <v>6616744</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19364,7 +19353,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>121735377</v>
+        <v>121735531</v>
       </c>
       <c r="B171" t="n">
         <v>98113</v>
@@ -19399,7 +19388,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -19418,10 +19407,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>685440</v>
+        <v>685357</v>
       </c>
       <c r="R171" t="n">
-        <v>6616805</v>
+        <v>6616798</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19480,7 +19469,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121734849</v>
+        <v>121735485</v>
       </c>
       <c r="B172" t="n">
         <v>98113</v>
@@ -19515,7 +19504,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>78</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -19525,19 +19514,21 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>685480</v>
+        <v>685409</v>
       </c>
       <c r="R172" t="n">
-        <v>6616744</v>
+        <v>6616795</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19572,12 +19563,18 @@
           <t>2024-12-25</t>
         </is>
       </c>
+      <c r="AC172" t="inlineStr">
+        <is>
+          <t>4 blomställningar</t>
+        </is>
+      </c>
       <c r="AD172" t="b">
         <v>0</v>
       </c>
       <c r="AE172" t="b">
         <v>0</v>
       </c>
+      <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="b">
         <v>0</v>
       </c>
@@ -19596,7 +19593,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>121735074</v>
+        <v>121735377</v>
       </c>
       <c r="B173" t="n">
         <v>98113</v>
@@ -19631,7 +19628,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -19650,10 +19647,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>685486</v>
+        <v>685440</v>
       </c>
       <c r="R173" t="n">
-        <v>6616781</v>
+        <v>6616805</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19712,7 +19709,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>121735498</v>
+        <v>121734727</v>
       </c>
       <c r="B174" t="n">
         <v>98113</v>
@@ -19747,7 +19744,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -19760,16 +19757,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L174" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>685410</v>
+        <v>685481</v>
       </c>
       <c r="R174" t="n">
-        <v>6616808</v>
+        <v>6616734</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19810,6 +19809,7 @@
       <c r="AE174" t="b">
         <v>0</v>
       </c>
+      <c r="AF174" t="inlineStr"/>
       <c r="AG174" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -18668,7 +18668,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121735074</v>
+        <v>121735498</v>
       </c>
       <c r="B165" t="n">
         <v>98113</v>
@@ -18703,7 +18703,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -18722,10 +18722,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>685486</v>
+        <v>685410</v>
       </c>
       <c r="R165" t="n">
-        <v>6616781</v>
+        <v>6616808</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18784,7 +18784,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121735498</v>
+        <v>121734849</v>
       </c>
       <c r="B166" t="n">
         <v>98113</v>
@@ -18819,7 +18819,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -18838,10 +18838,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>685410</v>
+        <v>685480</v>
       </c>
       <c r="R166" t="n">
-        <v>6616808</v>
+        <v>6616744</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18900,7 +18900,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121735325</v>
+        <v>121734727</v>
       </c>
       <c r="B167" t="n">
         <v>98113</v>
@@ -18935,7 +18935,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -18956,10 +18956,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>685448</v>
+        <v>685481</v>
       </c>
       <c r="R167" t="n">
-        <v>6616789</v>
+        <v>6616734</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19019,7 +19019,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121734849</v>
+        <v>121735531</v>
       </c>
       <c r="B168" t="n">
         <v>98113</v>
@@ -19054,7 +19054,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -19073,10 +19073,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>685480</v>
+        <v>685357</v>
       </c>
       <c r="R168" t="n">
-        <v>6616744</v>
+        <v>6616798</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19135,10 +19135,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>121735416</v>
+        <v>121733071</v>
       </c>
       <c r="B169" t="n">
-        <v>98113</v>
+        <v>90748</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -19147,52 +19147,38 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J169" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>685413</v>
+        <v>685246</v>
       </c>
       <c r="R169" t="n">
-        <v>6616793</v>
+        <v>6616659</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19251,10 +19237,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>121733071</v>
+        <v>121735377</v>
       </c>
       <c r="B170" t="n">
-        <v>90748</v>
+        <v>98113</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -19263,38 +19249,52 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>685246</v>
+        <v>685440</v>
       </c>
       <c r="R170" t="n">
-        <v>6616659</v>
+        <v>6616805</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19353,7 +19353,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>121735531</v>
+        <v>121734887</v>
       </c>
       <c r="B171" t="n">
         <v>98113</v>
@@ -19388,7 +19388,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -19407,10 +19407,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>685357</v>
+        <v>685475</v>
       </c>
       <c r="R171" t="n">
-        <v>6616798</v>
+        <v>6616757</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19593,7 +19593,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>121735377</v>
+        <v>121735416</v>
       </c>
       <c r="B173" t="n">
         <v>98113</v>
@@ -19628,7 +19628,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -19647,10 +19647,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>685440</v>
+        <v>685413</v>
       </c>
       <c r="R173" t="n">
-        <v>6616805</v>
+        <v>6616793</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19709,7 +19709,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>121734727</v>
+        <v>121735325</v>
       </c>
       <c r="B174" t="n">
         <v>98113</v>
@@ -19744,7 +19744,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -19765,10 +19765,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>685481</v>
+        <v>685448</v>
       </c>
       <c r="R174" t="n">
-        <v>6616734</v>
+        <v>6616789</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19828,7 +19828,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>121734887</v>
+        <v>121735074</v>
       </c>
       <c r="B175" t="n">
         <v>98113</v>
@@ -19863,7 +19863,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -19882,10 +19882,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>685475</v>
+        <v>685486</v>
       </c>
       <c r="R175" t="n">
-        <v>6616757</v>
+        <v>6616781</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -18668,7 +18668,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121735498</v>
+        <v>121735377</v>
       </c>
       <c r="B165" t="n">
         <v>98113</v>
@@ -18703,7 +18703,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -18722,10 +18722,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>685410</v>
+        <v>685440</v>
       </c>
       <c r="R165" t="n">
-        <v>6616808</v>
+        <v>6616805</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18784,7 +18784,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121734849</v>
+        <v>121735074</v>
       </c>
       <c r="B166" t="n">
         <v>98113</v>
@@ -18819,7 +18819,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -18838,10 +18838,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>685480</v>
+        <v>685486</v>
       </c>
       <c r="R166" t="n">
-        <v>6616744</v>
+        <v>6616781</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19019,7 +19019,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121735531</v>
+        <v>121734887</v>
       </c>
       <c r="B168" t="n">
         <v>98113</v>
@@ -19054,7 +19054,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -19073,10 +19073,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>685357</v>
+        <v>685475</v>
       </c>
       <c r="R168" t="n">
-        <v>6616798</v>
+        <v>6616757</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19135,10 +19135,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>121733071</v>
+        <v>121734849</v>
       </c>
       <c r="B169" t="n">
-        <v>90748</v>
+        <v>98113</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -19147,38 +19147,52 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>685246</v>
+        <v>685480</v>
       </c>
       <c r="R169" t="n">
-        <v>6616659</v>
+        <v>6616744</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19237,7 +19251,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>121735377</v>
+        <v>121735531</v>
       </c>
       <c r="B170" t="n">
         <v>98113</v>
@@ -19272,7 +19286,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -19291,10 +19305,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>685440</v>
+        <v>685357</v>
       </c>
       <c r="R170" t="n">
-        <v>6616805</v>
+        <v>6616798</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19353,10 +19367,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>121734887</v>
+        <v>121733071</v>
       </c>
       <c r="B171" t="n">
-        <v>98113</v>
+        <v>90748</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -19365,52 +19379,38 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J171" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>685475</v>
+        <v>685246</v>
       </c>
       <c r="R171" t="n">
-        <v>6616757</v>
+        <v>6616659</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19469,7 +19469,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121735485</v>
+        <v>121735498</v>
       </c>
       <c r="B172" t="n">
         <v>98113</v>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -19514,21 +19514,19 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L172" t="inlineStr"/>
-      <c r="N172" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P172" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>685409</v>
+        <v>685410</v>
       </c>
       <c r="R172" t="n">
-        <v>6616795</v>
+        <v>6616808</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19563,18 +19561,12 @@
           <t>2024-12-25</t>
         </is>
       </c>
-      <c r="AC172" t="inlineStr">
-        <is>
-          <t>4 blomställningar</t>
-        </is>
-      </c>
       <c r="AD172" t="b">
         <v>0</v>
       </c>
       <c r="AE172" t="b">
         <v>0</v>
       </c>
-      <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="b">
         <v>0</v>
       </c>
@@ -19828,7 +19820,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>121735074</v>
+        <v>121735485</v>
       </c>
       <c r="B175" t="n">
         <v>98113</v>
@@ -19863,7 +19855,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>78</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -19873,19 +19865,21 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>685486</v>
+        <v>685409</v>
       </c>
       <c r="R175" t="n">
-        <v>6616781</v>
+        <v>6616795</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19920,12 +19914,18 @@
           <t>2024-12-25</t>
         </is>
       </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>4 blomställningar</t>
+        </is>
+      </c>
       <c r="AD175" t="b">
         <v>0</v>
       </c>
       <c r="AE175" t="b">
         <v>0</v>
       </c>
+      <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="b">
         <v>0</v>
       </c>
@@ -19944,7 +19944,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>121743769</v>
+        <v>121734526</v>
       </c>
       <c r="B176" t="n">
         <v>98113</v>
@@ -19979,7 +19979,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>57</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -20000,10 +20000,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>685401</v>
+        <v>685452</v>
       </c>
       <c r="R176" t="n">
-        <v>6616722</v>
+        <v>6616694</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -20030,17 +20030,17 @@
       </c>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-12-25</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-12-25</t>
         </is>
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>Återbesök</t>
+          <t>Återbesök. Kring en äldre tall.</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -20192,7 +20192,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>121734526</v>
+        <v>121743769</v>
       </c>
       <c r="B178" t="n">
         <v>98113</v>
@@ -20227,7 +20227,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -20248,10 +20248,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>685452</v>
+        <v>685401</v>
       </c>
       <c r="R178" t="n">
-        <v>6616694</v>
+        <v>6616722</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20278,17 +20278,17 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>Återbesök. Kring en äldre tall.</t>
+          <t>Återbesök</t>
         </is>
       </c>
       <c r="AD178" t="b">

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -18668,7 +18668,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121735377</v>
+        <v>121734849</v>
       </c>
       <c r="B165" t="n">
         <v>98113</v>
@@ -18703,7 +18703,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -18722,10 +18722,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>685440</v>
+        <v>685480</v>
       </c>
       <c r="R165" t="n">
-        <v>6616805</v>
+        <v>6616744</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18784,7 +18784,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121735074</v>
+        <v>121734727</v>
       </c>
       <c r="B166" t="n">
         <v>98113</v>
@@ -18819,7 +18819,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -18832,16 +18832,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L166" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>685486</v>
+        <v>685481</v>
       </c>
       <c r="R166" t="n">
-        <v>6616781</v>
+        <v>6616734</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18882,6 +18884,7 @@
       <c r="AE166" t="b">
         <v>0</v>
       </c>
+      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
       </c>
@@ -18900,10 +18903,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121734727</v>
+        <v>121733071</v>
       </c>
       <c r="B167" t="n">
-        <v>98113</v>
+        <v>90748</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18912,54 +18915,38 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L167" t="inlineStr"/>
-      <c r="N167" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>685481</v>
+        <v>685246</v>
       </c>
       <c r="R167" t="n">
-        <v>6616734</v>
+        <v>6616659</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19000,7 +18987,6 @@
       <c r="AE167" t="b">
         <v>0</v>
       </c>
-      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
@@ -19019,7 +19005,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121734887</v>
+        <v>121735074</v>
       </c>
       <c r="B168" t="n">
         <v>98113</v>
@@ -19054,7 +19040,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -19073,10 +19059,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>685475</v>
+        <v>685486</v>
       </c>
       <c r="R168" t="n">
-        <v>6616757</v>
+        <v>6616781</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19135,7 +19121,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>121734849</v>
+        <v>121735377</v>
       </c>
       <c r="B169" t="n">
         <v>98113</v>
@@ -19170,7 +19156,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -19189,10 +19175,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>685480</v>
+        <v>685440</v>
       </c>
       <c r="R169" t="n">
-        <v>6616744</v>
+        <v>6616805</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19251,7 +19237,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>121735531</v>
+        <v>121734887</v>
       </c>
       <c r="B170" t="n">
         <v>98113</v>
@@ -19286,7 +19272,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -19305,10 +19291,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>685357</v>
+        <v>685475</v>
       </c>
       <c r="R170" t="n">
-        <v>6616798</v>
+        <v>6616757</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19367,10 +19353,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>121733071</v>
+        <v>121735416</v>
       </c>
       <c r="B171" t="n">
-        <v>90748</v>
+        <v>98113</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -19379,38 +19365,52 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>685246</v>
+        <v>685413</v>
       </c>
       <c r="R171" t="n">
-        <v>6616659</v>
+        <v>6616793</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19585,7 +19585,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>121735416</v>
+        <v>121735485</v>
       </c>
       <c r="B173" t="n">
         <v>98113</v>
@@ -19620,7 +19620,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>78</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -19630,19 +19630,21 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr"/>
+      <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>685413</v>
+        <v>685409</v>
       </c>
       <c r="R173" t="n">
-        <v>6616793</v>
+        <v>6616795</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19677,12 +19679,18 @@
           <t>2024-12-25</t>
         </is>
       </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>4 blomställningar</t>
+        </is>
+      </c>
       <c r="AD173" t="b">
         <v>0</v>
       </c>
       <c r="AE173" t="b">
         <v>0</v>
       </c>
+      <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="b">
         <v>0</v>
       </c>
@@ -19701,7 +19709,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>121735325</v>
+        <v>121735531</v>
       </c>
       <c r="B174" t="n">
         <v>98113</v>
@@ -19736,7 +19744,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -19749,18 +19757,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L174" t="inlineStr"/>
-      <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>685448</v>
+        <v>685357</v>
       </c>
       <c r="R174" t="n">
-        <v>6616789</v>
+        <v>6616798</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19801,7 +19807,6 @@
       <c r="AE174" t="b">
         <v>0</v>
       </c>
-      <c r="AF174" t="inlineStr"/>
       <c r="AG174" t="b">
         <v>0</v>
       </c>
@@ -19820,7 +19825,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>121735485</v>
+        <v>121735325</v>
       </c>
       <c r="B175" t="n">
         <v>98113</v>
@@ -19855,7 +19860,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -19865,7 +19870,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L175" t="inlineStr"/>
@@ -19876,10 +19881,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>685409</v>
+        <v>685448</v>
       </c>
       <c r="R175" t="n">
-        <v>6616795</v>
+        <v>6616789</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19912,11 +19917,6 @@
       <c r="AA175" t="inlineStr">
         <is>
           <t>2024-12-25</t>
-        </is>
-      </c>
-      <c r="AC175" t="inlineStr">
-        <is>
-          <t>4 blomställningar</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19944,7 +19944,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>121734526</v>
+        <v>121743769</v>
       </c>
       <c r="B176" t="n">
         <v>98113</v>
@@ -19979,7 +19979,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -20000,10 +20000,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>685452</v>
+        <v>685401</v>
       </c>
       <c r="R176" t="n">
-        <v>6616694</v>
+        <v>6616722</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -20030,17 +20030,17 @@
       </c>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>Återbesök. Kring en äldre tall.</t>
+          <t>Återbesök</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -20192,7 +20192,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>121743769</v>
+        <v>121734526</v>
       </c>
       <c r="B178" t="n">
         <v>98113</v>
@@ -20227,7 +20227,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>57</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -20248,10 +20248,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>685401</v>
+        <v>685452</v>
       </c>
       <c r="R178" t="n">
-        <v>6616722</v>
+        <v>6616694</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20278,17 +20278,17 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-12-25</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-12-25</t>
         </is>
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>Återbesök</t>
+          <t>Återbesök. Kring en äldre tall.</t>
         </is>
       </c>
       <c r="AD178" t="b">

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -16586,7 +16586,7 @@
         <v>120741868</v>
       </c>
       <c r="B147" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -17056,7 +17056,7 @@
         <v>120741991</v>
       </c>
       <c r="B151" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17758,7 +17758,7 @@
         <v>120761028</v>
       </c>
       <c r="B157" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -18668,10 +18668,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121734849</v>
+        <v>121733071</v>
       </c>
       <c r="B165" t="n">
-        <v>98113</v>
+        <v>90762</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18680,52 +18680,38 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>685480</v>
+        <v>685246</v>
       </c>
       <c r="R165" t="n">
-        <v>6616744</v>
+        <v>6616659</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18784,10 +18770,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121734727</v>
+        <v>121735416</v>
       </c>
       <c r="B166" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -18819,7 +18805,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -18832,18 +18818,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L166" t="inlineStr"/>
-      <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>685481</v>
+        <v>685413</v>
       </c>
       <c r="R166" t="n">
-        <v>6616734</v>
+        <v>6616793</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18884,7 +18868,6 @@
       <c r="AE166" t="b">
         <v>0</v>
       </c>
-      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
       </c>
@@ -18903,10 +18886,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121733071</v>
+        <v>121735531</v>
       </c>
       <c r="B167" t="n">
-        <v>90748</v>
+        <v>98131</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18915,38 +18898,52 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>685246</v>
+        <v>685357</v>
       </c>
       <c r="R167" t="n">
-        <v>6616659</v>
+        <v>6616798</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19005,10 +19002,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121735074</v>
+        <v>121734887</v>
       </c>
       <c r="B168" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -19040,7 +19037,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -19059,10 +19056,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>685486</v>
+        <v>685475</v>
       </c>
       <c r="R168" t="n">
-        <v>6616781</v>
+        <v>6616757</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19121,10 +19118,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>121735377</v>
+        <v>121734727</v>
       </c>
       <c r="B169" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -19156,7 +19153,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -19169,16 +19166,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>685440</v>
+        <v>685481</v>
       </c>
       <c r="R169" t="n">
-        <v>6616805</v>
+        <v>6616734</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19219,6 +19218,7 @@
       <c r="AE169" t="b">
         <v>0</v>
       </c>
+      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
@@ -19237,10 +19237,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>121734887</v>
+        <v>121735498</v>
       </c>
       <c r="B170" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -19272,7 +19272,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -19291,10 +19291,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>685475</v>
+        <v>685410</v>
       </c>
       <c r="R170" t="n">
-        <v>6616757</v>
+        <v>6616808</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19353,10 +19353,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>121735416</v>
+        <v>121735485</v>
       </c>
       <c r="B171" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -19388,7 +19388,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>78</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -19398,19 +19398,21 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>685413</v>
+        <v>685409</v>
       </c>
       <c r="R171" t="n">
-        <v>6616793</v>
+        <v>6616795</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19445,12 +19447,18 @@
           <t>2024-12-25</t>
         </is>
       </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>4 blomställningar</t>
+        </is>
+      </c>
       <c r="AD171" t="b">
         <v>0</v>
       </c>
       <c r="AE171" t="b">
         <v>0</v>
       </c>
+      <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="b">
         <v>0</v>
       </c>
@@ -19469,10 +19477,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121735498</v>
+        <v>121735325</v>
       </c>
       <c r="B172" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -19504,7 +19512,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -19517,16 +19525,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>685410</v>
+        <v>685448</v>
       </c>
       <c r="R172" t="n">
-        <v>6616808</v>
+        <v>6616789</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19567,6 +19577,7 @@
       <c r="AE172" t="b">
         <v>0</v>
       </c>
+      <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="b">
         <v>0</v>
       </c>
@@ -19585,10 +19596,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>121735485</v>
+        <v>121735074</v>
       </c>
       <c r="B173" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -19620,7 +19631,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -19630,21 +19641,19 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L173" t="inlineStr"/>
-      <c r="N173" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P173" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>685409</v>
+        <v>685486</v>
       </c>
       <c r="R173" t="n">
-        <v>6616795</v>
+        <v>6616781</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19679,18 +19688,12 @@
           <t>2024-12-25</t>
         </is>
       </c>
-      <c r="AC173" t="inlineStr">
-        <is>
-          <t>4 blomställningar</t>
-        </is>
-      </c>
       <c r="AD173" t="b">
         <v>0</v>
       </c>
       <c r="AE173" t="b">
         <v>0</v>
       </c>
-      <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="b">
         <v>0</v>
       </c>
@@ -19709,10 +19712,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>121735531</v>
+        <v>121735377</v>
       </c>
       <c r="B174" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -19744,7 +19747,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -19763,10 +19766,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>685357</v>
+        <v>685440</v>
       </c>
       <c r="R174" t="n">
-        <v>6616798</v>
+        <v>6616805</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19825,10 +19828,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>121735325</v>
+        <v>121734849</v>
       </c>
       <c r="B175" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -19860,7 +19863,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -19873,18 +19876,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>685448</v>
+        <v>685480</v>
       </c>
       <c r="R175" t="n">
-        <v>6616789</v>
+        <v>6616744</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19925,7 +19926,6 @@
       <c r="AE175" t="b">
         <v>0</v>
       </c>
-      <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="b">
         <v>0</v>
       </c>
@@ -19947,7 +19947,7 @@
         <v>121743769</v>
       </c>
       <c r="B176" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -20071,7 +20071,7 @@
         <v>121735053</v>
       </c>
       <c r="B177" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>121734526</v>
       </c>
       <c r="B178" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -20319,7 +20319,7 @@
         <v>121762495</v>
       </c>
       <c r="B179" t="n">
-        <v>90746</v>
+        <v>90760</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY179"/>
+  <dimension ref="A1:AY178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14235,10 +14235,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>115031352</v>
+        <v>115031254</v>
       </c>
       <c r="B126" t="n">
-        <v>96604</v>
+        <v>74640</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14247,37 +14247,41 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>221944</v>
+        <v>308</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr"/>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Upl</t>
+          <t>Gransumpskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>685317</v>
+        <v>685365</v>
       </c>
       <c r="R126" t="n">
-        <v>6616684</v>
+        <v>6616656</v>
       </c>
       <c r="S126" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -14333,10 +14337,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>115031254</v>
+        <v>115046432</v>
       </c>
       <c r="B127" t="n">
-        <v>74640</v>
+        <v>90350</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14349,21 +14353,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>308</v>
+        <v>5432</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14373,7 +14377,7 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>685365</v>
+        <v>685381</v>
       </c>
       <c r="R127" t="n">
         <v>6616656</v>
@@ -14403,12 +14407,12 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2024-03-06</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2024-03-06</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14435,10 +14439,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>115046432</v>
+        <v>115046040</v>
       </c>
       <c r="B128" t="n">
-        <v>90350</v>
+        <v>90332</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14451,21 +14455,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14475,7 +14479,7 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>685381</v>
+        <v>685365</v>
       </c>
       <c r="R128" t="n">
         <v>6616656</v>
@@ -14537,10 +14541,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>115046040</v>
+        <v>115137366</v>
       </c>
       <c r="B129" t="n">
-        <v>90332</v>
+        <v>74640</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14553,34 +14557,37 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Gransumpskog nordväst om Tjärdalen, Upl</t>
+          <t>Gransumpskog sydost om Kårsta, Upl</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>685365</v>
+        <v>685394</v>
       </c>
       <c r="R129" t="n">
-        <v>6616656</v>
+        <v>6616766</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14607,12 +14614,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2024-03-07</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2024-03-07</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14621,6 +14628,7 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -14639,10 +14647,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>115137366</v>
+        <v>115338429</v>
       </c>
       <c r="B130" t="n">
-        <v>74640</v>
+        <v>90350</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14655,40 +14663,37 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>308</v>
+        <v>5432</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Gransumpskog sydost om Kårsta, Upl</t>
+          <t>Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>685394</v>
+        <v>685346</v>
       </c>
       <c r="R130" t="n">
-        <v>6616766</v>
+        <v>6616716</v>
       </c>
       <c r="S130" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14712,12 +14717,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14726,7 +14731,6 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -14745,10 +14749,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>115338429</v>
+        <v>115338216</v>
       </c>
       <c r="B131" t="n">
-        <v>90350</v>
+        <v>96613</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14757,25 +14761,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5432</v>
+        <v>221946</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14785,10 +14789,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>685346</v>
+        <v>685332</v>
       </c>
       <c r="R131" t="n">
-        <v>6616716</v>
+        <v>6616685</v>
       </c>
       <c r="S131" t="n">
         <v>20</v>
@@ -14847,10 +14851,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>115338216</v>
+        <v>115699045</v>
       </c>
       <c r="B132" t="n">
-        <v>96613</v>
+        <v>57414</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14859,41 +14863,45 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>221946</v>
+        <v>103021</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Upl</t>
+          <t>Gransumpskog 1 km sydost om Kårsta, Upl</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>685332</v>
+        <v>685306</v>
       </c>
       <c r="R132" t="n">
-        <v>6616685</v>
+        <v>6616677</v>
       </c>
       <c r="S132" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14917,12 +14925,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14949,10 +14957,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>115699045</v>
+        <v>118717859</v>
       </c>
       <c r="B133" t="n">
-        <v>57414</v>
+        <v>98605</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14965,41 +14973,51 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>103021</v>
+        <v>222361</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Gransumpskog 1 km sydost om Kårsta, Upl</t>
+          <t>Barrnaturskog 750m OSO om Bergsjön (Nordväst om Tjärdalen), Upl</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>685306</v>
+        <v>685385</v>
       </c>
       <c r="R133" t="n">
-        <v>6616677</v>
+        <v>6616774</v>
       </c>
       <c r="S133" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -15023,12 +15041,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15055,10 +15073,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>118717859</v>
+        <v>120061670</v>
       </c>
       <c r="B134" t="n">
-        <v>98605</v>
+        <v>97930</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -15067,30 +15085,30 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>222361</v>
+        <v>220787</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -15100,19 +15118,19 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Barrnaturskog 750m OSO om Bergsjön (Nordväst om Tjärdalen), Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>685385</v>
+        <v>685428</v>
       </c>
       <c r="R134" t="n">
-        <v>6616774</v>
+        <v>6616738</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15139,12 +15157,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15171,7 +15189,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120061670</v>
+        <v>120061796</v>
       </c>
       <c r="B135" t="n">
         <v>97930</v>
@@ -15206,7 +15224,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -15216,7 +15234,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -15225,10 +15243,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>685428</v>
+        <v>685429</v>
       </c>
       <c r="R135" t="n">
-        <v>6616738</v>
+        <v>6616759</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15261,6 +15279,11 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>En blomställning</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15287,7 +15310,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120061796</v>
+        <v>120061896</v>
       </c>
       <c r="B136" t="n">
         <v>97930</v>
@@ -15322,7 +15345,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>71</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -15332,7 +15355,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
@@ -15341,10 +15364,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>685429</v>
+        <v>685406</v>
       </c>
       <c r="R136" t="n">
-        <v>6616759</v>
+        <v>6616750</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15377,11 +15400,6 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>En blomställning</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15408,7 +15426,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120061896</v>
+        <v>120061280</v>
       </c>
       <c r="B137" t="n">
         <v>97930</v>
@@ -15443,7 +15461,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -15458,14 +15476,14 @@
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>685406</v>
+        <v>685380</v>
       </c>
       <c r="R137" t="n">
-        <v>6616750</v>
+        <v>6616654</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15524,7 +15542,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>120061280</v>
+        <v>120061391</v>
       </c>
       <c r="B138" t="n">
         <v>97930</v>
@@ -15559,7 +15577,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -15578,10 +15596,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>685380</v>
+        <v>685384</v>
       </c>
       <c r="R138" t="n">
-        <v>6616654</v>
+        <v>6616661</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15640,7 +15658,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>120061391</v>
+        <v>120061691</v>
       </c>
       <c r="B139" t="n">
         <v>97930</v>
@@ -15675,7 +15693,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -15690,14 +15708,14 @@
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>685384</v>
+        <v>685447</v>
       </c>
       <c r="R139" t="n">
-        <v>6616661</v>
+        <v>6616746</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15756,7 +15774,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>120061691</v>
+        <v>120062150</v>
       </c>
       <c r="B140" t="n">
         <v>97930</v>
@@ -15791,7 +15809,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -15801,19 +15819,19 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>685447</v>
+        <v>685379</v>
       </c>
       <c r="R140" t="n">
-        <v>6616746</v>
+        <v>6616654</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15846,6 +15864,11 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15872,7 +15895,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>120062150</v>
+        <v>120061814</v>
       </c>
       <c r="B141" t="n">
         <v>97930</v>
@@ -15907,7 +15930,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -15917,19 +15940,19 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
+          <t>Gransumpskog sydost om Kårsta, Gransumpskog sydost om Kårsta, Upl</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>685379</v>
+        <v>685421</v>
       </c>
       <c r="R141" t="n">
-        <v>6616654</v>
+        <v>6616765</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15962,11 +15985,6 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15993,10 +16011,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>120061814</v>
+        <v>119812067</v>
       </c>
       <c r="B142" t="n">
-        <v>97930</v>
+        <v>90151</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -16005,52 +16023,41 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>220787</v>
+        <v>5741</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Gransumpskog sydost om Kårsta, Gransumpskog sydost om Kårsta, Upl</t>
+          <t>Barrnaturskog nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>685421</v>
+        <v>685340</v>
       </c>
       <c r="R142" t="n">
-        <v>6616765</v>
+        <v>6616746</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16077,12 +16084,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16091,6 +16098,7 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
+      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -16109,10 +16117,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>119812067</v>
+        <v>120713578</v>
       </c>
       <c r="B143" t="n">
-        <v>90151</v>
+        <v>91338</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -16121,25 +16129,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5741</v>
+        <v>898</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -16148,17 +16156,17 @@
       <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Barrnaturskog nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Kårsta byskog, Upl</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>685340</v>
+        <v>685300</v>
       </c>
       <c r="R143" t="n">
-        <v>6616746</v>
+        <v>6616654</v>
       </c>
       <c r="S143" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -16182,12 +16190,17 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-10-27</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-10-27</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>Exkursion med Botaniska Sällskapet i Sthlm samt Naturskyddsföreningen Vallentuna.</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16200,25 +16213,45 @@
       <c r="AG143" t="b">
         <v>0</v>
       </c>
+      <c r="AH143" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
+      </c>
+      <c r="AJ143" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK143" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO143" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Lisel Hamring</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Lisel Hamring</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>120713578</v>
+        <v>120742091</v>
       </c>
       <c r="B144" t="n">
-        <v>91338</v>
+        <v>98059</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16231,40 +16264,51 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>898</v>
+        <v>220787</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Kårsta byskog, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>685300</v>
+        <v>685249</v>
       </c>
       <c r="R144" t="n">
-        <v>6616654</v>
+        <v>6616652</v>
       </c>
       <c r="S144" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -16288,17 +16332,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
-        </is>
-      </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>Exkursion med Botaniska Sällskapet i Sthlm samt Naturskyddsföreningen Vallentuna.</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16307,46 +16346,25 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
-      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
-      </c>
-      <c r="AH144" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
-      </c>
-      <c r="AJ144" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK144" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO144" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Lisel Hamring</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Lisel Hamring</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>120742091</v>
+        <v>120742594</v>
       </c>
       <c r="B145" t="n">
         <v>98059</v>
@@ -16381,7 +16399,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -16391,7 +16409,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -16400,10 +16418,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>685249</v>
+        <v>685278</v>
       </c>
       <c r="R145" t="n">
-        <v>6616652</v>
+        <v>6616713</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16436,6 +16454,11 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16462,10 +16485,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>120742594</v>
+        <v>120741868</v>
       </c>
       <c r="B146" t="n">
-        <v>98059</v>
+        <v>98133</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16497,7 +16520,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -16507,19 +16530,21 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog nordväst om Tjärdalen, Barrnaturskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>685278</v>
+        <v>685307</v>
       </c>
       <c r="R146" t="n">
-        <v>6616713</v>
+        <v>6616649</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16554,17 +16579,13 @@
           <t>2024-10-29</t>
         </is>
       </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>2 blomställningar</t>
-        </is>
-      </c>
       <c r="AD146" t="b">
         <v>0</v>
       </c>
       <c r="AE146" t="b">
         <v>0</v>
       </c>
+      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
@@ -16583,10 +16604,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>120741868</v>
+        <v>120742485</v>
       </c>
       <c r="B147" t="n">
-        <v>98131</v>
+        <v>98059</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16631,18 +16652,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L147" t="inlineStr"/>
-      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Barrnaturskog nordväst om Tjärdalen, Barrnaturskog nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>685307</v>
+        <v>685276</v>
       </c>
       <c r="R147" t="n">
-        <v>6616649</v>
+        <v>6616670</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16683,7 +16702,6 @@
       <c r="AE147" t="b">
         <v>0</v>
       </c>
-      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
       </c>
@@ -16702,7 +16720,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>120742485</v>
+        <v>120742626</v>
       </c>
       <c r="B148" t="n">
         <v>98059</v>
@@ -16737,7 +16755,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -16747,7 +16765,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
@@ -16756,10 +16774,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>685276</v>
+        <v>685263</v>
       </c>
       <c r="R148" t="n">
-        <v>6616670</v>
+        <v>6616724</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16818,7 +16836,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>120742626</v>
+        <v>120742252</v>
       </c>
       <c r="B149" t="n">
         <v>98059</v>
@@ -16853,7 +16871,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -16863,19 +16881,21 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>685263</v>
+        <v>685253</v>
       </c>
       <c r="R149" t="n">
-        <v>6616724</v>
+        <v>6616665</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16916,6 +16936,7 @@
       <c r="AE149" t="b">
         <v>0</v>
       </c>
+      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
@@ -16934,10 +16955,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>120742252</v>
+        <v>120741991</v>
       </c>
       <c r="B150" t="n">
-        <v>98059</v>
+        <v>98133</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16969,7 +16990,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -16986,14 +17007,14 @@
       <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Gransumpskog 1 km sydost om Kårsta, Gransumpskog 1 km sydost om Kårsta, Upl</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>685253</v>
+        <v>685302</v>
       </c>
       <c r="R150" t="n">
-        <v>6616665</v>
+        <v>6616679</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17053,10 +17074,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>120741991</v>
+        <v>120759925</v>
       </c>
       <c r="B151" t="n">
-        <v>98131</v>
+        <v>98071</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17088,7 +17109,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -17101,18 +17122,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L151" t="inlineStr"/>
-      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Gransumpskog 1 km sydost om Kårsta, Gransumpskog 1 km sydost om Kårsta, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>685302</v>
+        <v>685296</v>
       </c>
       <c r="R151" t="n">
-        <v>6616679</v>
+        <v>6616725</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17139,12 +17158,12 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17153,7 +17172,6 @@
       <c r="AE151" t="b">
         <v>0</v>
       </c>
-      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
@@ -17172,7 +17190,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>120759925</v>
+        <v>120760778</v>
       </c>
       <c r="B152" t="n">
         <v>98071</v>
@@ -17207,7 +17225,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -17226,10 +17244,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>685296</v>
+        <v>685370</v>
       </c>
       <c r="R152" t="n">
-        <v>6616725</v>
+        <v>6616785</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17288,7 +17306,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>120760778</v>
+        <v>120760174</v>
       </c>
       <c r="B153" t="n">
         <v>98071</v>
@@ -17323,7 +17341,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -17336,16 +17354,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>685370</v>
+        <v>685346</v>
       </c>
       <c r="R153" t="n">
-        <v>6616785</v>
+        <v>6616758</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17386,6 +17406,7 @@
       <c r="AE153" t="b">
         <v>0</v>
       </c>
+      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
@@ -17404,7 +17425,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>120760174</v>
+        <v>120759986</v>
       </c>
       <c r="B154" t="n">
         <v>98071</v>
@@ -17439,7 +17460,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -17452,18 +17473,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L154" t="inlineStr"/>
-      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>685346</v>
+        <v>685342</v>
       </c>
       <c r="R154" t="n">
-        <v>6616758</v>
+        <v>6616736</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17504,7 +17523,6 @@
       <c r="AE154" t="b">
         <v>0</v>
       </c>
-      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
       </c>
@@ -17523,7 +17541,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>120759986</v>
+        <v>120759914</v>
       </c>
       <c r="B155" t="n">
         <v>98071</v>
@@ -17558,7 +17576,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>213</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -17577,10 +17595,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>685342</v>
+        <v>685311</v>
       </c>
       <c r="R155" t="n">
-        <v>6616736</v>
+        <v>6616724</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17639,10 +17657,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>120759914</v>
+        <v>120761028</v>
       </c>
       <c r="B156" t="n">
-        <v>98071</v>
+        <v>98133</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17674,7 +17692,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -17687,16 +17705,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>685311</v>
+        <v>685433</v>
       </c>
       <c r="R156" t="n">
-        <v>6616724</v>
+        <v>6616678</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17723,12 +17743,12 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-12-25</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-12-25</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17737,6 +17757,7 @@
       <c r="AE156" t="b">
         <v>0</v>
       </c>
+      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
@@ -17755,10 +17776,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>120761028</v>
+        <v>120761260</v>
       </c>
       <c r="B157" t="n">
-        <v>98131</v>
+        <v>98071</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17790,7 +17811,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -17803,18 +17824,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L157" t="inlineStr"/>
-      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>685433</v>
+        <v>685438</v>
       </c>
       <c r="R157" t="n">
-        <v>6616678</v>
+        <v>6616696</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17841,12 +17860,12 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17855,7 +17874,6 @@
       <c r="AE157" t="b">
         <v>0</v>
       </c>
-      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
@@ -17874,7 +17892,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>120761260</v>
+        <v>120760861</v>
       </c>
       <c r="B158" t="n">
         <v>98071</v>
@@ -17909,7 +17927,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -17928,10 +17946,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>685438</v>
+        <v>685381</v>
       </c>
       <c r="R158" t="n">
-        <v>6616696</v>
+        <v>6616734</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17990,7 +18008,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>120760861</v>
+        <v>120760830</v>
       </c>
       <c r="B159" t="n">
         <v>98071</v>
@@ -18025,7 +18043,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -18044,10 +18062,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>685381</v>
+        <v>685374</v>
       </c>
       <c r="R159" t="n">
-        <v>6616734</v>
+        <v>6616755</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18106,7 +18124,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>120760830</v>
+        <v>120760736</v>
       </c>
       <c r="B160" t="n">
         <v>98071</v>
@@ -18141,7 +18159,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -18151,7 +18169,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
@@ -18160,10 +18178,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>685374</v>
+        <v>685370</v>
       </c>
       <c r="R160" t="n">
-        <v>6616755</v>
+        <v>6616803</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18196,6 +18214,11 @@
       <c r="AA160" t="inlineStr">
         <is>
           <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>1 blomställning</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18222,10 +18245,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>120760736</v>
+        <v>120836325</v>
       </c>
       <c r="B161" t="n">
-        <v>98071</v>
+        <v>98098</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -18257,7 +18280,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -18267,19 +18290,19 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog nordväst om Tjärdalen, Barrnaturskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>685370</v>
+        <v>685314</v>
       </c>
       <c r="R161" t="n">
-        <v>6616803</v>
+        <v>6616738</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18306,17 +18329,12 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
-        </is>
-      </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>1 blomställning</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18343,10 +18361,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>120836325</v>
+        <v>121343884</v>
       </c>
       <c r="B162" t="n">
-        <v>98098</v>
+        <v>97059</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18355,52 +18373,38 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>220787</v>
+        <v>224361</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Barrnaturskog nordväst om Tjärdalen, Barrnaturskog nordväst om Tjärdalen, Upl</t>
+          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>685314</v>
+        <v>685317</v>
       </c>
       <c r="R162" t="n">
-        <v>6616738</v>
+        <v>6616676</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18427,12 +18431,12 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18459,10 +18463,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121343884</v>
+        <v>121567592</v>
       </c>
       <c r="B163" t="n">
-        <v>97059</v>
+        <v>8436</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -18475,34 +18479,39 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>224361</v>
+        <v>106545</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>685317</v>
+        <v>685437</v>
       </c>
       <c r="R163" t="n">
-        <v>6616676</v>
+        <v>6616649</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18529,12 +18538,12 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18561,10 +18570,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121567592</v>
+        <v>121735485</v>
       </c>
       <c r="B164" t="n">
-        <v>8436</v>
+        <v>98133</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -18573,43 +18582,54 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr"/>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>685437</v>
+        <v>685409</v>
       </c>
       <c r="R164" t="n">
-        <v>6616649</v>
+        <v>6616795</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18636,12 +18656,17 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2024-12-25</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2024-12-25</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>4 blomställningar</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18650,6 +18675,7 @@
       <c r="AE164" t="b">
         <v>0</v>
       </c>
+      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
@@ -18668,10 +18694,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121733071</v>
+        <v>121734727</v>
       </c>
       <c r="B165" t="n">
-        <v>90762</v>
+        <v>98133</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18680,38 +18706,54 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>685246</v>
+        <v>685481</v>
       </c>
       <c r="R165" t="n">
-        <v>6616659</v>
+        <v>6616734</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18752,6 +18794,7 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
+      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
@@ -18770,10 +18813,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121735416</v>
+        <v>121734887</v>
       </c>
       <c r="B166" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -18805,7 +18848,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -18824,10 +18867,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>685413</v>
+        <v>685475</v>
       </c>
       <c r="R166" t="n">
-        <v>6616793</v>
+        <v>6616757</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18886,10 +18929,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121735531</v>
+        <v>121735416</v>
       </c>
       <c r="B167" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18921,7 +18964,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -18940,10 +18983,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>685357</v>
+        <v>685413</v>
       </c>
       <c r="R167" t="n">
-        <v>6616798</v>
+        <v>6616793</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19002,10 +19045,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121734887</v>
+        <v>121734849</v>
       </c>
       <c r="B168" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -19037,7 +19080,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -19056,10 +19099,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>685475</v>
+        <v>685480</v>
       </c>
       <c r="R168" t="n">
-        <v>6616757</v>
+        <v>6616744</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19118,10 +19161,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>121734727</v>
+        <v>121735531</v>
       </c>
       <c r="B169" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -19153,7 +19196,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -19166,18 +19209,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>685481</v>
+        <v>685357</v>
       </c>
       <c r="R169" t="n">
-        <v>6616734</v>
+        <v>6616798</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19218,7 +19259,6 @@
       <c r="AE169" t="b">
         <v>0</v>
       </c>
-      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
@@ -19237,10 +19277,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>121735498</v>
+        <v>121735325</v>
       </c>
       <c r="B170" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -19272,7 +19312,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -19285,16 +19325,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>685410</v>
+        <v>685448</v>
       </c>
       <c r="R170" t="n">
-        <v>6616808</v>
+        <v>6616789</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19335,6 +19377,7 @@
       <c r="AE170" t="b">
         <v>0</v>
       </c>
+      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
       </c>
@@ -19353,10 +19396,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>121735485</v>
+        <v>121735498</v>
       </c>
       <c r="B171" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -19388,7 +19431,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -19398,21 +19441,19 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L171" t="inlineStr"/>
-      <c r="N171" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P171" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>685409</v>
+        <v>685410</v>
       </c>
       <c r="R171" t="n">
-        <v>6616795</v>
+        <v>6616808</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19447,18 +19488,12 @@
           <t>2024-12-25</t>
         </is>
       </c>
-      <c r="AC171" t="inlineStr">
-        <is>
-          <t>4 blomställningar</t>
-        </is>
-      </c>
       <c r="AD171" t="b">
         <v>0</v>
       </c>
       <c r="AE171" t="b">
         <v>0</v>
       </c>
-      <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="b">
         <v>0</v>
       </c>
@@ -19477,10 +19512,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121735325</v>
+        <v>121735074</v>
       </c>
       <c r="B172" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -19512,7 +19547,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -19525,18 +19560,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L172" t="inlineStr"/>
-      <c r="N172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>685448</v>
+        <v>685486</v>
       </c>
       <c r="R172" t="n">
-        <v>6616789</v>
+        <v>6616781</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19577,7 +19610,6 @@
       <c r="AE172" t="b">
         <v>0</v>
       </c>
-      <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="b">
         <v>0</v>
       </c>
@@ -19596,10 +19628,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>121735074</v>
+        <v>121733071</v>
       </c>
       <c r="B173" t="n">
-        <v>98131</v>
+        <v>90764</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -19608,52 +19640,38 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>685486</v>
+        <v>685246</v>
       </c>
       <c r="R173" t="n">
-        <v>6616781</v>
+        <v>6616659</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19715,7 +19733,7 @@
         <v>121735377</v>
       </c>
       <c r="B174" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -19828,10 +19846,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>121734849</v>
+        <v>121734526</v>
       </c>
       <c r="B175" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -19863,7 +19881,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>57</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -19876,16 +19894,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>685480</v>
+        <v>685452</v>
       </c>
       <c r="R175" t="n">
-        <v>6616744</v>
+        <v>6616694</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19920,12 +19940,18 @@
           <t>2024-12-25</t>
         </is>
       </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>Återbesök. Kring en äldre tall.</t>
+        </is>
+      </c>
       <c r="AD175" t="b">
         <v>0</v>
       </c>
       <c r="AE175" t="b">
         <v>0</v>
       </c>
+      <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="b">
         <v>0</v>
       </c>
@@ -19944,10 +19970,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>121743769</v>
+        <v>121735053</v>
       </c>
       <c r="B176" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -19979,7 +20005,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>242</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -19989,7 +20015,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L176" t="inlineStr"/>
@@ -20000,10 +20026,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>685401</v>
+        <v>685473</v>
       </c>
       <c r="R176" t="n">
-        <v>6616722</v>
+        <v>6616791</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -20030,17 +20056,17 @@
       </c>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-12-25</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-12-25</t>
         </is>
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>Återbesök</t>
+          <t>En blomställning</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -20068,10 +20094,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>121735053</v>
+        <v>121743769</v>
       </c>
       <c r="B177" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -20103,7 +20129,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -20113,7 +20139,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L177" t="inlineStr"/>
@@ -20124,10 +20150,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>685473</v>
+        <v>685401</v>
       </c>
       <c r="R177" t="n">
-        <v>6616791</v>
+        <v>6616722</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -20154,17 +20180,17 @@
       </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>En blomställning</t>
+          <t>Återbesök</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20192,10 +20218,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>121734526</v>
+        <v>121762495</v>
       </c>
       <c r="B178" t="n">
-        <v>98131</v>
+        <v>90762</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -20204,54 +20230,38 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L178" t="inlineStr"/>
-      <c r="N178" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>685452</v>
+        <v>685252</v>
       </c>
       <c r="R178" t="n">
-        <v>6616694</v>
+        <v>6616654</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20278,17 +20288,12 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
-        </is>
-      </c>
-      <c r="AC178" t="inlineStr">
-        <is>
-          <t>Återbesök. Kring en äldre tall.</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -20297,7 +20302,6 @@
       <c r="AE178" t="b">
         <v>0</v>
       </c>
-      <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="b">
         <v>0</v>
       </c>
@@ -20313,108 +20317,6 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
-    </row>
-    <row r="179">
-      <c r="A179" t="n">
-        <v>121762495</v>
-      </c>
-      <c r="B179" t="n">
-        <v>90760</v>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E179" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr"/>
-      <c r="P179" t="inlineStr">
-        <is>
-          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
-        </is>
-      </c>
-      <c r="Q179" t="n">
-        <v>685252</v>
-      </c>
-      <c r="R179" t="n">
-        <v>6616654</v>
-      </c>
-      <c r="S179" t="n">
-        <v>10</v>
-      </c>
-      <c r="T179" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U179" t="inlineStr">
-        <is>
-          <t>Vallentuna</t>
-        </is>
-      </c>
-      <c r="V179" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W179" t="inlineStr">
-        <is>
-          <t>Kårsta</t>
-        </is>
-      </c>
-      <c r="Y179" t="inlineStr">
-        <is>
-          <t>2024-12-28</t>
-        </is>
-      </c>
-      <c r="AA179" t="inlineStr">
-        <is>
-          <t>2024-12-28</t>
-        </is>
-      </c>
-      <c r="AD179" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE179" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG179" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT179" t="inlineStr"/>
-      <c r="AW179" t="inlineStr">
-        <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AX179" t="inlineStr">
-        <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY179" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -16488,7 +16488,7 @@
         <v>120741868</v>
       </c>
       <c r="B146" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16958,7 +16958,7 @@
         <v>120741991</v>
       </c>
       <c r="B150" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>120761028</v>
       </c>
       <c r="B156" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -18570,10 +18570,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121735485</v>
+        <v>121735416</v>
       </c>
       <c r="B164" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -18605,7 +18605,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -18615,21 +18615,19 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P164" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>685409</v>
+        <v>685413</v>
       </c>
       <c r="R164" t="n">
-        <v>6616795</v>
+        <v>6616793</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18664,18 +18662,12 @@
           <t>2024-12-25</t>
         </is>
       </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>4 blomställningar</t>
-        </is>
-      </c>
       <c r="AD164" t="b">
         <v>0</v>
       </c>
       <c r="AE164" t="b">
         <v>0</v>
       </c>
-      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
@@ -18694,10 +18686,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121734727</v>
+        <v>121735531</v>
       </c>
       <c r="B165" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18729,7 +18721,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -18742,18 +18734,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>685481</v>
+        <v>685357</v>
       </c>
       <c r="R165" t="n">
-        <v>6616734</v>
+        <v>6616798</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18794,7 +18784,6 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
-      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
@@ -18813,10 +18802,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121734887</v>
+        <v>121735074</v>
       </c>
       <c r="B166" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -18848,7 +18837,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -18867,10 +18856,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>685475</v>
+        <v>685486</v>
       </c>
       <c r="R166" t="n">
-        <v>6616757</v>
+        <v>6616781</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18929,10 +18918,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121735416</v>
+        <v>121735325</v>
       </c>
       <c r="B167" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18964,7 +18953,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -18977,16 +18966,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>685413</v>
+        <v>685448</v>
       </c>
       <c r="R167" t="n">
-        <v>6616793</v>
+        <v>6616789</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19027,6 +19018,7 @@
       <c r="AE167" t="b">
         <v>0</v>
       </c>
+      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
@@ -19045,10 +19037,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121734849</v>
+        <v>121734727</v>
       </c>
       <c r="B168" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -19080,7 +19072,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -19093,16 +19085,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>685480</v>
+        <v>685481</v>
       </c>
       <c r="R168" t="n">
-        <v>6616744</v>
+        <v>6616734</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19143,6 +19137,7 @@
       <c r="AE168" t="b">
         <v>0</v>
       </c>
+      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
@@ -19161,10 +19156,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>121735531</v>
+        <v>121735485</v>
       </c>
       <c r="B169" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -19196,7 +19191,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>78</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -19206,19 +19201,21 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>685357</v>
+        <v>685409</v>
       </c>
       <c r="R169" t="n">
-        <v>6616798</v>
+        <v>6616795</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19253,12 +19250,18 @@
           <t>2024-12-25</t>
         </is>
       </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>4 blomställningar</t>
+        </is>
+      </c>
       <c r="AD169" t="b">
         <v>0</v>
       </c>
       <c r="AE169" t="b">
         <v>0</v>
       </c>
+      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
@@ -19277,10 +19280,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>121735325</v>
+        <v>121735377</v>
       </c>
       <c r="B170" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -19312,7 +19315,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -19325,18 +19328,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L170" t="inlineStr"/>
-      <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>685448</v>
+        <v>685440</v>
       </c>
       <c r="R170" t="n">
-        <v>6616789</v>
+        <v>6616805</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19377,7 +19378,6 @@
       <c r="AE170" t="b">
         <v>0</v>
       </c>
-      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
       </c>
@@ -19396,10 +19396,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>121735498</v>
+        <v>121733071</v>
       </c>
       <c r="B171" t="n">
-        <v>98133</v>
+        <v>90765</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -19408,52 +19408,38 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J171" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>685410</v>
+        <v>685246</v>
       </c>
       <c r="R171" t="n">
-        <v>6616808</v>
+        <v>6616659</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19512,10 +19498,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121735074</v>
+        <v>121734887</v>
       </c>
       <c r="B172" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -19547,7 +19533,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -19566,10 +19552,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>685486</v>
+        <v>685475</v>
       </c>
       <c r="R172" t="n">
-        <v>6616781</v>
+        <v>6616757</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19628,10 +19614,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>121733071</v>
+        <v>121735498</v>
       </c>
       <c r="B173" t="n">
-        <v>90764</v>
+        <v>98140</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -19640,38 +19626,52 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>685246</v>
+        <v>685410</v>
       </c>
       <c r="R173" t="n">
-        <v>6616659</v>
+        <v>6616808</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19730,10 +19730,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>121735377</v>
+        <v>121734849</v>
       </c>
       <c r="B174" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -19765,7 +19765,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -19784,10 +19784,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>685440</v>
+        <v>685480</v>
       </c>
       <c r="R174" t="n">
-        <v>6616805</v>
+        <v>6616744</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19846,10 +19846,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>121734526</v>
+        <v>121735053</v>
       </c>
       <c r="B175" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -19881,7 +19881,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>242</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -19891,7 +19891,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L175" t="inlineStr"/>
@@ -19902,10 +19902,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>685452</v>
+        <v>685473</v>
       </c>
       <c r="R175" t="n">
-        <v>6616694</v>
+        <v>6616791</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19942,7 +19942,7 @@
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>Återbesök. Kring en äldre tall.</t>
+          <t>En blomställning</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19970,10 +19970,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>121735053</v>
+        <v>121734526</v>
       </c>
       <c r="B176" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -20005,7 +20005,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>57</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -20015,7 +20015,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L176" t="inlineStr"/>
@@ -20026,10 +20026,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>685473</v>
+        <v>685452</v>
       </c>
       <c r="R176" t="n">
-        <v>6616791</v>
+        <v>6616694</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -20066,7 +20066,7 @@
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>En blomställning</t>
+          <t>Återbesök. Kring en äldre tall.</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -20097,7 +20097,7 @@
         <v>121743769</v>
       </c>
       <c r="B177" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -20221,7 +20221,7 @@
         <v>121762495</v>
       </c>
       <c r="B178" t="n">
-        <v>90762</v>
+        <v>90763</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -16488,7 +16488,7 @@
         <v>120741868</v>
       </c>
       <c r="B146" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16958,7 +16958,7 @@
         <v>120741991</v>
       </c>
       <c r="B150" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>120761028</v>
       </c>
       <c r="B156" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -18570,10 +18570,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121735416</v>
+        <v>121735325</v>
       </c>
       <c r="B164" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -18605,7 +18605,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -18618,16 +18618,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>685413</v>
+        <v>685448</v>
       </c>
       <c r="R164" t="n">
-        <v>6616793</v>
+        <v>6616789</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18668,6 +18670,7 @@
       <c r="AE164" t="b">
         <v>0</v>
       </c>
+      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
@@ -18686,10 +18689,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121735531</v>
+        <v>121734887</v>
       </c>
       <c r="B165" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18721,7 +18724,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -18740,10 +18743,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>685357</v>
+        <v>685475</v>
       </c>
       <c r="R165" t="n">
-        <v>6616798</v>
+        <v>6616757</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18802,10 +18805,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121735074</v>
+        <v>121735485</v>
       </c>
       <c r="B166" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -18837,7 +18840,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>78</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -18847,19 +18850,21 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>685486</v>
+        <v>685409</v>
       </c>
       <c r="R166" t="n">
-        <v>6616781</v>
+        <v>6616795</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18894,12 +18899,18 @@
           <t>2024-12-25</t>
         </is>
       </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>4 blomställningar</t>
+        </is>
+      </c>
       <c r="AD166" t="b">
         <v>0</v>
       </c>
       <c r="AE166" t="b">
         <v>0</v>
       </c>
+      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
       </c>
@@ -18918,10 +18929,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121735325</v>
+        <v>121734727</v>
       </c>
       <c r="B167" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18953,7 +18964,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -18974,10 +18985,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>685448</v>
+        <v>685481</v>
       </c>
       <c r="R167" t="n">
-        <v>6616789</v>
+        <v>6616734</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19037,10 +19048,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121734727</v>
+        <v>121734849</v>
       </c>
       <c r="B168" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -19072,7 +19083,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -19085,18 +19096,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L168" t="inlineStr"/>
-      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>685481</v>
+        <v>685480</v>
       </c>
       <c r="R168" t="n">
-        <v>6616734</v>
+        <v>6616744</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19137,7 +19146,6 @@
       <c r="AE168" t="b">
         <v>0</v>
       </c>
-      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
@@ -19156,10 +19164,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>121735485</v>
+        <v>121735498</v>
       </c>
       <c r="B169" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -19191,7 +19199,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -19201,21 +19209,19 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P169" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>685409</v>
+        <v>685410</v>
       </c>
       <c r="R169" t="n">
-        <v>6616795</v>
+        <v>6616808</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19250,18 +19256,12 @@
           <t>2024-12-25</t>
         </is>
       </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>4 blomställningar</t>
-        </is>
-      </c>
       <c r="AD169" t="b">
         <v>0</v>
       </c>
       <c r="AE169" t="b">
         <v>0</v>
       </c>
-      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
@@ -19280,10 +19280,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>121735377</v>
+        <v>121735074</v>
       </c>
       <c r="B170" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -19315,7 +19315,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -19334,10 +19334,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>685440</v>
+        <v>685486</v>
       </c>
       <c r="R170" t="n">
-        <v>6616805</v>
+        <v>6616781</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19396,10 +19396,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>121733071</v>
+        <v>121735416</v>
       </c>
       <c r="B171" t="n">
-        <v>90765</v>
+        <v>98149</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -19408,38 +19408,52 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>685246</v>
+        <v>685413</v>
       </c>
       <c r="R171" t="n">
-        <v>6616659</v>
+        <v>6616793</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19498,10 +19512,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121734887</v>
+        <v>121735377</v>
       </c>
       <c r="B172" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -19533,7 +19547,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -19552,10 +19566,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>685475</v>
+        <v>685440</v>
       </c>
       <c r="R172" t="n">
-        <v>6616757</v>
+        <v>6616805</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19614,10 +19628,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>121735498</v>
+        <v>121733071</v>
       </c>
       <c r="B173" t="n">
-        <v>98140</v>
+        <v>90774</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -19626,52 +19640,38 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>685410</v>
+        <v>685246</v>
       </c>
       <c r="R173" t="n">
-        <v>6616808</v>
+        <v>6616659</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19730,10 +19730,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>121734849</v>
+        <v>121735531</v>
       </c>
       <c r="B174" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -19765,7 +19765,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -19784,10 +19784,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>685480</v>
+        <v>685357</v>
       </c>
       <c r="R174" t="n">
-        <v>6616744</v>
+        <v>6616798</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19846,10 +19846,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>121735053</v>
+        <v>121743769</v>
       </c>
       <c r="B175" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -19881,7 +19881,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -19891,7 +19891,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L175" t="inlineStr"/>
@@ -19902,10 +19902,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>685473</v>
+        <v>685401</v>
       </c>
       <c r="R175" t="n">
-        <v>6616791</v>
+        <v>6616722</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19932,17 +19932,17 @@
       </c>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>En blomställning</t>
+          <t>Återbesök</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19973,7 +19973,7 @@
         <v>121734526</v>
       </c>
       <c r="B176" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -20094,10 +20094,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>121743769</v>
+        <v>121735053</v>
       </c>
       <c r="B177" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -20129,7 +20129,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>242</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L177" t="inlineStr"/>
@@ -20150,10 +20150,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>685401</v>
+        <v>685473</v>
       </c>
       <c r="R177" t="n">
-        <v>6616722</v>
+        <v>6616791</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -20180,17 +20180,17 @@
       </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-12-25</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-12-25</t>
         </is>
       </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>Återbesök</t>
+          <t>En blomställning</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20221,7 +20221,7 @@
         <v>121762495</v>
       </c>
       <c r="B178" t="n">
-        <v>90763</v>
+        <v>90772</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY178"/>
+  <dimension ref="A1:AY179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20318,6 +20318,108 @@
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>122380531</v>
+      </c>
+      <c r="B179" t="n">
+        <v>94599</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>2813</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus subpinnatus</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr"/>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>Barrnaturskog 800m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q179" t="n">
+        <v>685355</v>
+      </c>
+      <c r="R179" t="n">
+        <v>6616740</v>
+      </c>
+      <c r="S179" t="n">
+        <v>10</v>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W179" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AD179" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE179" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG179" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT179" t="inlineStr"/>
+      <c r="AW179" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX179" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY179" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -20323,7 +20323,7 @@
         <v>122380531</v>
       </c>
       <c r="B179" t="n">
-        <v>94599</v>
+        <v>94611</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -20323,7 +20323,7 @@
         <v>122380531</v>
       </c>
       <c r="B179" t="n">
-        <v>94611</v>
+        <v>94616</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -20323,7 +20323,7 @@
         <v>122380531</v>
       </c>
       <c r="B179" t="n">
-        <v>94616</v>
+        <v>94625</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -20337,11 +20337,6 @@
       </c>
       <c r="E179" t="n">
         <v>2813</v>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>Skogshakmossa</t>
-        </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -20323,7 +20323,7 @@
         <v>122380531</v>
       </c>
       <c r="B179" t="n">
-        <v>94625</v>
+        <v>94638</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -20337,6 +20337,11 @@
       </c>
       <c r="E179" t="n">
         <v>2813</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Skogshakmossa</t>
+        </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -20323,7 +20323,7 @@
         <v>122380531</v>
       </c>
       <c r="B179" t="n">
-        <v>94638</v>
+        <v>94651</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -20323,7 +20323,7 @@
         <v>122380531</v>
       </c>
       <c r="B179" t="n">
-        <v>94651</v>
+        <v>94653</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -20323,7 +20323,7 @@
         <v>122380531</v>
       </c>
       <c r="B179" t="n">
-        <v>94653</v>
+        <v>94654</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -20323,7 +20323,7 @@
         <v>122380531</v>
       </c>
       <c r="B179" t="n">
-        <v>94654</v>
+        <v>94657</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -20425,7 +20425,7 @@
         <v>122775468</v>
       </c>
       <c r="B180" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -20425,7 +20425,7 @@
         <v>122775468</v>
       </c>
       <c r="B180" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -20425,7 +20425,7 @@
         <v>122775468</v>
       </c>
       <c r="B180" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY180"/>
+  <dimension ref="A1:AY181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20551,6 +20551,117 @@
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>123282824</v>
+      </c>
+      <c r="B181" t="n">
+        <v>57631</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>Barrnaturskog 700m SO Bergsjön , Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q181" t="n">
+        <v>685357</v>
+      </c>
+      <c r="R181" t="n">
+        <v>6616766</v>
+      </c>
+      <c r="S181" t="n">
+        <v>25</v>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W181" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AD181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT181" t="inlineStr"/>
+      <c r="AW181" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX181" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY181" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY181"/>
+  <dimension ref="A1:AY182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20662,6 +20662,112 @@
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>123282215</v>
+      </c>
+      <c r="B182" t="n">
+        <v>74849</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>306</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Kornig nållav</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Chaenotheca chlorella</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="N182" t="inlineStr"/>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>Barrnaturskog 800m SO Bergsjön , Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q182" t="n">
+        <v>685329</v>
+      </c>
+      <c r="R182" t="n">
+        <v>6616644</v>
+      </c>
+      <c r="S182" t="n">
+        <v>10</v>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AD182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF182" t="inlineStr"/>
+      <c r="AG182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT182" t="inlineStr"/>
+      <c r="AW182" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX182" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY182" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -20425,7 +20425,7 @@
         <v>122775468</v>
       </c>
       <c r="B180" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -20556,7 +20556,7 @@
         <v>123282824</v>
       </c>
       <c r="B181" t="n">
-        <v>57631</v>
+        <v>57634</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -20667,7 +20667,7 @@
         <v>123282215</v>
       </c>
       <c r="B182" t="n">
-        <v>74849</v>
+        <v>74852</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -20425,7 +20425,7 @@
         <v>122775468</v>
       </c>
       <c r="B180" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -20425,7 +20425,7 @@
         <v>122775468</v>
       </c>
       <c r="B180" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -20556,7 +20556,7 @@
         <v>123282824</v>
       </c>
       <c r="B181" t="n">
-        <v>57634</v>
+        <v>57640</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -20667,7 +20667,7 @@
         <v>123282215</v>
       </c>
       <c r="B182" t="n">
-        <v>74855</v>
+        <v>74861</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -20773,7 +20773,7 @@
         <v>123662940</v>
       </c>
       <c r="B183" t="n">
-        <v>94996</v>
+        <v>95013</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -20556,7 +20556,7 @@
         <v>123282824</v>
       </c>
       <c r="B181" t="n">
-        <v>57640</v>
+        <v>57643</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -20667,7 +20667,7 @@
         <v>123282215</v>
       </c>
       <c r="B182" t="n">
-        <v>74861</v>
+        <v>74864</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -20773,7 +20773,7 @@
         <v>123662940</v>
       </c>
       <c r="B183" t="n">
-        <v>95013</v>
+        <v>95019</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -20556,7 +20556,7 @@
         <v>123282824</v>
       </c>
       <c r="B181" t="n">
-        <v>57643</v>
+        <v>57644</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -20667,7 +20667,7 @@
         <v>123282215</v>
       </c>
       <c r="B182" t="n">
-        <v>74864</v>
+        <v>74865</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -20773,7 +20773,7 @@
         <v>123662940</v>
       </c>
       <c r="B183" t="n">
-        <v>95019</v>
+        <v>95021</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -20773,7 +20773,7 @@
         <v>123662940</v>
       </c>
       <c r="B183" t="n">
-        <v>95021</v>
+        <v>95529</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY183"/>
+  <dimension ref="A1:AY184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20883,6 +20883,122 @@
       </c>
       <c r="AY183" t="inlineStr"/>
     </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>125443813</v>
+      </c>
+      <c r="B184" t="n">
+        <v>98122</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>Barrnaturskog nordväst om Tjärdalen, Barrnaturskog nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q184" t="n">
+        <v>685328</v>
+      </c>
+      <c r="R184" t="n">
+        <v>6616664</v>
+      </c>
+      <c r="S184" t="n">
+        <v>10</v>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT184" t="inlineStr"/>
+      <c r="AW184" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX184" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY184" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -20888,7 +20888,7 @@
         <v>125443813</v>
       </c>
       <c r="B184" t="n">
-        <v>98122</v>
+        <v>98290</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -20888,12 +20888,7 @@
         <v>125443813</v>
       </c>
       <c r="B184" t="n">
-        <v>98290</v>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98345</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -20888,7 +20888,7 @@
         <v>125443813</v>
       </c>
       <c r="B184" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -20888,7 +20888,7 @@
         <v>125443813</v>
       </c>
       <c r="B184" t="n">
-        <v>98352</v>
+        <v>98355</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -20888,7 +20888,7 @@
         <v>125443813</v>
       </c>
       <c r="B184" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -20888,7 +20888,7 @@
         <v>125443813</v>
       </c>
       <c r="B184" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -20888,7 +20888,7 @@
         <v>125443813</v>
       </c>
       <c r="B184" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY185"/>
+  <dimension ref="A1:AY186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20999,7 +20999,7 @@
         <v>126668423</v>
       </c>
       <c r="B185" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21099,6 +21099,103 @@
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>127043186</v>
+      </c>
+      <c r="B186" t="n">
+        <v>95800</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr"/>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>Gransumpskog 700m OSO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q186" t="n">
+        <v>685389</v>
+      </c>
+      <c r="R186" t="n">
+        <v>6616746</v>
+      </c>
+      <c r="S186" t="n">
+        <v>10</v>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AD186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT186" t="inlineStr"/>
+      <c r="AW186" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX186" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY186" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -20999,7 +20999,7 @@
         <v>126668423</v>
       </c>
       <c r="B185" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21104,7 +21104,7 @@
         <v>127043186</v>
       </c>
       <c r="B186" t="n">
-        <v>95800</v>
+        <v>95802</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -21104,7 +21104,7 @@
         <v>127043186</v>
       </c>
       <c r="B186" t="n">
-        <v>95802</v>
+        <v>95808</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -21104,7 +21104,7 @@
         <v>127043186</v>
       </c>
       <c r="B186" t="n">
-        <v>95808</v>
+        <v>95811</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -21104,7 +21104,7 @@
         <v>127043186</v>
       </c>
       <c r="B186" t="n">
-        <v>95811</v>
+        <v>95819</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -21104,7 +21104,7 @@
         <v>127043186</v>
       </c>
       <c r="B186" t="n">
-        <v>95819</v>
+        <v>95820</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -21104,7 +21104,7 @@
         <v>127043186</v>
       </c>
       <c r="B186" t="n">
-        <v>95820</v>
+        <v>95821</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -21104,7 +21104,7 @@
         <v>127043186</v>
       </c>
       <c r="B186" t="n">
-        <v>95821</v>
+        <v>95822</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY186"/>
+  <dimension ref="A1:AY192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21196,6 +21196,598 @@
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>128610913</v>
+      </c>
+      <c r="B187" t="n">
+        <v>95803</v>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr"/>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>Barrnaturskog 700m O Bergsjön, Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q187" t="n">
+        <v>685398</v>
+      </c>
+      <c r="R187" t="n">
+        <v>6616729</v>
+      </c>
+      <c r="S187" t="n">
+        <v>10</v>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y187" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT187" t="inlineStr"/>
+      <c r="AW187" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX187" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>128611241</v>
+      </c>
+      <c r="B188" t="n">
+        <v>90961</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>5741</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Tjockfotad fingersvamp</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Ramaria flavescens</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr"/>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>Barrnaturskog 700m O Bergsjön, Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q188" t="n">
+        <v>685420</v>
+      </c>
+      <c r="R188" t="n">
+        <v>6616725</v>
+      </c>
+      <c r="S188" t="n">
+        <v>10</v>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W188" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y188" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT188" t="inlineStr"/>
+      <c r="AW188" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX188" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>128611191</v>
+      </c>
+      <c r="B189" t="n">
+        <v>90961</v>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>5741</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Tjockfotad fingersvamp</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Ramaria flavescens</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr"/>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>Barrnaturskog 700m O Bergsjön, Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q189" t="n">
+        <v>685428</v>
+      </c>
+      <c r="R189" t="n">
+        <v>6616695</v>
+      </c>
+      <c r="S189" t="n">
+        <v>10</v>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W189" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y189" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD189" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE189" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG189" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT189" t="inlineStr"/>
+      <c r="AW189" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX189" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>128611218</v>
+      </c>
+      <c r="B190" t="n">
+        <v>92731</v>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>150</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Grangråticka</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Boletopsis leucomelaena</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>Barrnaturskog 700m O Bergsjön, Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q190" t="n">
+        <v>685426</v>
+      </c>
+      <c r="R190" t="n">
+        <v>6616695</v>
+      </c>
+      <c r="S190" t="n">
+        <v>10</v>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W190" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y190" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC190" t="inlineStr">
+        <is>
+          <t>Återfynd</t>
+        </is>
+      </c>
+      <c r="AD190" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE190" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG190" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT190" t="inlineStr"/>
+      <c r="AW190" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX190" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>128610942</v>
+      </c>
+      <c r="B191" t="n">
+        <v>91225</v>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>Barrnaturskog 700m O Bergsjön, Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q191" t="n">
+        <v>685398</v>
+      </c>
+      <c r="R191" t="n">
+        <v>6616729</v>
+      </c>
+      <c r="S191" t="n">
+        <v>10</v>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W191" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y191" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD191" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE191" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG191" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT191" t="inlineStr"/>
+      <c r="AW191" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX191" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>128611030</v>
+      </c>
+      <c r="B192" t="n">
+        <v>86980</v>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>3624</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Strimspindling</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr"/>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>Barrnaturskog 700m O Bergsjön, Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q192" t="n">
+        <v>685411</v>
+      </c>
+      <c r="R192" t="n">
+        <v>6616715</v>
+      </c>
+      <c r="S192" t="n">
+        <v>10</v>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W192" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y192" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD192" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE192" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG192" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT192" t="inlineStr"/>
+      <c r="AW192" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX192" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY192" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY192"/>
+  <dimension ref="A1:AY193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21788,6 +21788,103 @@
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>128629864</v>
+      </c>
+      <c r="B193" t="n">
+        <v>86890</v>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>1988</v>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Kryddspindling</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Cortinarius percomis</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr"/>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q193" t="n">
+        <v>685354</v>
+      </c>
+      <c r="R193" t="n">
+        <v>6616772</v>
+      </c>
+      <c r="S193" t="n">
+        <v>10</v>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W193" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y193" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD193" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE193" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG193" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT193" t="inlineStr"/>
+      <c r="AW193" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX193" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY193" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -21201,7 +21201,7 @@
         <v>128610913</v>
       </c>
       <c r="B187" t="n">
-        <v>95803</v>
+        <v>95809</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21298,7 +21298,7 @@
         <v>128611241</v>
       </c>
       <c r="B188" t="n">
-        <v>90961</v>
+        <v>90967</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>128611191</v>
       </c>
       <c r="B189" t="n">
-        <v>90961</v>
+        <v>90967</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21492,7 +21492,7 @@
         <v>128611218</v>
       </c>
       <c r="B190" t="n">
-        <v>92731</v>
+        <v>92737</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>128610942</v>
       </c>
       <c r="B191" t="n">
-        <v>91225</v>
+        <v>91231</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21700,7 +21700,7 @@
         <v>128611030</v>
       </c>
       <c r="B192" t="n">
-        <v>86980</v>
+        <v>86985</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21793,7 +21793,7 @@
         <v>128629864</v>
       </c>
       <c r="B193" t="n">
-        <v>86890</v>
+        <v>86895</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -21201,7 +21201,7 @@
         <v>128610913</v>
       </c>
       <c r="B187" t="n">
-        <v>95809</v>
+        <v>95815</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21298,7 +21298,7 @@
         <v>128611241</v>
       </c>
       <c r="B188" t="n">
-        <v>90967</v>
+        <v>90973</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>128611191</v>
       </c>
       <c r="B189" t="n">
-        <v>90967</v>
+        <v>90973</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21492,7 +21492,7 @@
         <v>128611218</v>
       </c>
       <c r="B190" t="n">
-        <v>92737</v>
+        <v>92743</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>128610942</v>
       </c>
       <c r="B191" t="n">
-        <v>91231</v>
+        <v>91237</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21700,7 +21700,7 @@
         <v>128611030</v>
       </c>
       <c r="B192" t="n">
-        <v>86985</v>
+        <v>86991</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21793,7 +21793,7 @@
         <v>128629864</v>
       </c>
       <c r="B193" t="n">
-        <v>86895</v>
+        <v>86901</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -21201,7 +21201,7 @@
         <v>128610913</v>
       </c>
       <c r="B187" t="n">
-        <v>95815</v>
+        <v>95817</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21298,7 +21298,7 @@
         <v>128611241</v>
       </c>
       <c r="B188" t="n">
-        <v>90973</v>
+        <v>90975</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>128611191</v>
       </c>
       <c r="B189" t="n">
-        <v>90973</v>
+        <v>90975</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21492,7 +21492,7 @@
         <v>128611218</v>
       </c>
       <c r="B190" t="n">
-        <v>92743</v>
+        <v>92745</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>128610942</v>
       </c>
       <c r="B191" t="n">
-        <v>91237</v>
+        <v>91239</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21700,7 +21700,7 @@
         <v>128611030</v>
       </c>
       <c r="B192" t="n">
-        <v>86991</v>
+        <v>86993</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21793,7 +21793,7 @@
         <v>128629864</v>
       </c>
       <c r="B193" t="n">
-        <v>86901</v>
+        <v>86903</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -21201,7 +21201,7 @@
         <v>128610913</v>
       </c>
       <c r="B187" t="n">
-        <v>95817</v>
+        <v>95818</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21298,7 +21298,7 @@
         <v>128611241</v>
       </c>
       <c r="B188" t="n">
-        <v>90975</v>
+        <v>90976</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>128611191</v>
       </c>
       <c r="B189" t="n">
-        <v>90975</v>
+        <v>90976</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21492,7 +21492,7 @@
         <v>128611218</v>
       </c>
       <c r="B190" t="n">
-        <v>92745</v>
+        <v>92746</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>128610942</v>
       </c>
       <c r="B191" t="n">
-        <v>91239</v>
+        <v>91240</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -21201,7 +21201,7 @@
         <v>128610913</v>
       </c>
       <c r="B187" t="n">
-        <v>95818</v>
+        <v>95845</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21298,7 +21298,7 @@
         <v>128611241</v>
       </c>
       <c r="B188" t="n">
-        <v>90976</v>
+        <v>91003</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>128611191</v>
       </c>
       <c r="B189" t="n">
-        <v>90976</v>
+        <v>91003</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21492,7 +21492,7 @@
         <v>128611218</v>
       </c>
       <c r="B190" t="n">
-        <v>92746</v>
+        <v>92773</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>128610942</v>
       </c>
       <c r="B191" t="n">
-        <v>91240</v>
+        <v>91267</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21700,7 +21700,7 @@
         <v>128611030</v>
       </c>
       <c r="B192" t="n">
-        <v>86993</v>
+        <v>87020</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21793,7 +21793,7 @@
         <v>128629864</v>
       </c>
       <c r="B193" t="n">
-        <v>86903</v>
+        <v>86930</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -21201,7 +21201,7 @@
         <v>128610913</v>
       </c>
       <c r="B187" t="n">
-        <v>95845</v>
+        <v>95851</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21298,7 +21298,7 @@
         <v>128611241</v>
       </c>
       <c r="B188" t="n">
-        <v>91003</v>
+        <v>91008</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>128611191</v>
       </c>
       <c r="B189" t="n">
-        <v>91003</v>
+        <v>91008</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21492,7 +21492,7 @@
         <v>128611218</v>
       </c>
       <c r="B190" t="n">
-        <v>92773</v>
+        <v>92778</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>128610942</v>
       </c>
       <c r="B191" t="n">
-        <v>91267</v>
+        <v>91272</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21700,7 +21700,7 @@
         <v>128611030</v>
       </c>
       <c r="B192" t="n">
-        <v>87020</v>
+        <v>87024</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21793,7 +21793,7 @@
         <v>128629864</v>
       </c>
       <c r="B193" t="n">
-        <v>86930</v>
+        <v>86934</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -21201,7 +21201,7 @@
         <v>128610913</v>
       </c>
       <c r="B187" t="n">
-        <v>95851</v>
+        <v>95858</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21298,7 +21298,7 @@
         <v>128611241</v>
       </c>
       <c r="B188" t="n">
-        <v>91008</v>
+        <v>91013</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>128611191</v>
       </c>
       <c r="B189" t="n">
-        <v>91008</v>
+        <v>91013</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21492,7 +21492,7 @@
         <v>128611218</v>
       </c>
       <c r="B190" t="n">
-        <v>92778</v>
+        <v>92783</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>128610942</v>
       </c>
       <c r="B191" t="n">
-        <v>91272</v>
+        <v>91277</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21700,7 +21700,7 @@
         <v>128611030</v>
       </c>
       <c r="B192" t="n">
-        <v>87024</v>
+        <v>87025</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21793,7 +21793,7 @@
         <v>128629864</v>
       </c>
       <c r="B193" t="n">
-        <v>86934</v>
+        <v>86935</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -21201,7 +21201,7 @@
         <v>128610913</v>
       </c>
       <c r="B187" t="n">
-        <v>95858</v>
+        <v>95862</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21298,7 +21298,7 @@
         <v>128611241</v>
       </c>
       <c r="B188" t="n">
-        <v>91013</v>
+        <v>91017</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>128611191</v>
       </c>
       <c r="B189" t="n">
-        <v>91013</v>
+        <v>91017</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21492,7 +21492,7 @@
         <v>128611218</v>
       </c>
       <c r="B190" t="n">
-        <v>92783</v>
+        <v>92787</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>128610942</v>
       </c>
       <c r="B191" t="n">
-        <v>91277</v>
+        <v>91281</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21700,7 +21700,7 @@
         <v>128611030</v>
       </c>
       <c r="B192" t="n">
-        <v>87025</v>
+        <v>87029</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21793,7 +21793,7 @@
         <v>128629864</v>
       </c>
       <c r="B193" t="n">
-        <v>86935</v>
+        <v>86939</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -21201,7 +21201,7 @@
         <v>128610913</v>
       </c>
       <c r="B187" t="n">
-        <v>95862</v>
+        <v>95869</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21298,7 +21298,7 @@
         <v>128611241</v>
       </c>
       <c r="B188" t="n">
-        <v>91017</v>
+        <v>91022</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>128611191</v>
       </c>
       <c r="B189" t="n">
-        <v>91017</v>
+        <v>91022</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21492,7 +21492,7 @@
         <v>128611218</v>
       </c>
       <c r="B190" t="n">
-        <v>92787</v>
+        <v>92792</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>128610942</v>
       </c>
       <c r="B191" t="n">
-        <v>91281</v>
+        <v>91286</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21700,7 +21700,7 @@
         <v>128611030</v>
       </c>
       <c r="B192" t="n">
-        <v>87029</v>
+        <v>87034</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21793,7 +21793,7 @@
         <v>128629864</v>
       </c>
       <c r="B193" t="n">
-        <v>86939</v>
+        <v>86944</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -21201,7 +21201,7 @@
         <v>128610913</v>
       </c>
       <c r="B187" t="n">
-        <v>95872</v>
+        <v>95877</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21298,7 +21298,7 @@
         <v>128611241</v>
       </c>
       <c r="B188" t="n">
-        <v>91024</v>
+        <v>91029</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>128611191</v>
       </c>
       <c r="B189" t="n">
-        <v>91024</v>
+        <v>91029</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21492,7 +21492,7 @@
         <v>128611218</v>
       </c>
       <c r="B190" t="n">
-        <v>92795</v>
+        <v>92800</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>128610942</v>
       </c>
       <c r="B191" t="n">
-        <v>91288</v>
+        <v>91293</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21700,7 +21700,7 @@
         <v>128611030</v>
       </c>
       <c r="B192" t="n">
-        <v>87036</v>
+        <v>87041</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21793,7 +21793,7 @@
         <v>128629864</v>
       </c>
       <c r="B193" t="n">
-        <v>86946</v>
+        <v>86951</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY193"/>
+  <dimension ref="A1:AY194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21201,7 +21201,7 @@
         <v>128610913</v>
       </c>
       <c r="B187" t="n">
-        <v>95877</v>
+        <v>95885</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21298,7 +21298,7 @@
         <v>128611241</v>
       </c>
       <c r="B188" t="n">
-        <v>91029</v>
+        <v>91035</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>128611191</v>
       </c>
       <c r="B189" t="n">
-        <v>91029</v>
+        <v>91035</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21492,7 +21492,7 @@
         <v>128611218</v>
       </c>
       <c r="B190" t="n">
-        <v>92800</v>
+        <v>92808</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>128610942</v>
       </c>
       <c r="B191" t="n">
-        <v>91293</v>
+        <v>91299</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21700,7 +21700,7 @@
         <v>128611030</v>
       </c>
       <c r="B192" t="n">
-        <v>87041</v>
+        <v>87047</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21793,7 +21793,7 @@
         <v>128629864</v>
       </c>
       <c r="B193" t="n">
-        <v>86951</v>
+        <v>86957</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21884,6 +21884,103 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>129184200</v>
+      </c>
+      <c r="B194" t="n">
+        <v>91738</v>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>1106</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Vågticka</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Osteina undosa</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>(Peck) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr"/>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>Barrnaturskog nordväst om Tjärdalen, Barrnaturskog nordväst om Tjärdalen, Upl</t>
+        </is>
+      </c>
+      <c r="Q194" t="n">
+        <v>685322</v>
+      </c>
+      <c r="R194" t="n">
+        <v>6616694</v>
+      </c>
+      <c r="S194" t="n">
+        <v>10</v>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W194" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y194" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AD194" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE194" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG194" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT194" t="inlineStr"/>
+      <c r="AW194" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX194" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY194" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -21793,7 +21793,7 @@
         <v>128629864</v>
       </c>
       <c r="B193" t="n">
-        <v>86957</v>
+        <v>86961</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21890,7 +21890,7 @@
         <v>129184200</v>
       </c>
       <c r="B194" t="n">
-        <v>91738</v>
+        <v>91745</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -21890,7 +21890,7 @@
         <v>129184200</v>
       </c>
       <c r="B194" t="n">
-        <v>91745</v>
+        <v>91752</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -21890,7 +21890,7 @@
         <v>129184200</v>
       </c>
       <c r="B194" t="n">
-        <v>91752</v>
+        <v>91754</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -21890,7 +21890,7 @@
         <v>129184200</v>
       </c>
       <c r="B194" t="n">
-        <v>91754</v>
+        <v>91763</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -21890,7 +21890,7 @@
         <v>129184200</v>
       </c>
       <c r="B194" t="n">
-        <v>91763</v>
+        <v>91764</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -21890,7 +21890,7 @@
         <v>129184200</v>
       </c>
       <c r="B194" t="n">
-        <v>91764</v>
+        <v>91767</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -21890,7 +21890,7 @@
         <v>129184200</v>
       </c>
       <c r="B194" t="n">
-        <v>91767</v>
+        <v>91769</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -21890,7 +21890,7 @@
         <v>129184200</v>
       </c>
       <c r="B194" t="n">
-        <v>91769</v>
+        <v>91773</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -21890,7 +21890,7 @@
         <v>129184200</v>
       </c>
       <c r="B194" t="n">
-        <v>91773</v>
+        <v>91774</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -21890,7 +21890,7 @@
         <v>129184200</v>
       </c>
       <c r="B194" t="n">
-        <v>91774</v>
+        <v>91777</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -21890,7 +21890,7 @@
         <v>129184200</v>
       </c>
       <c r="B194" t="n">
-        <v>91777</v>
+        <v>91805</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY194"/>
+  <dimension ref="A1:AY195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21982,6 +21982,104 @@
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>129675381</v>
+      </c>
+      <c r="B195" t="n">
+        <v>95994</v>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr"/>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>Kårstabyskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q195" t="n">
+        <v>685347</v>
+      </c>
+      <c r="R195" t="n">
+        <v>6616663</v>
+      </c>
+      <c r="S195" t="n">
+        <v>10</v>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W195" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y195" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF195" t="inlineStr"/>
+      <c r="AG195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT195" t="inlineStr"/>
+      <c r="AW195" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX195" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY195" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -21987,7 +21987,7 @@
         <v>129675381</v>
       </c>
       <c r="B195" t="n">
-        <v>95994</v>
+        <v>95995</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -21987,7 +21987,7 @@
         <v>129675381</v>
       </c>
       <c r="B195" t="n">
-        <v>95995</v>
+        <v>96000</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -21987,7 +21987,7 @@
         <v>129675381</v>
       </c>
       <c r="B195" t="n">
-        <v>96000</v>
+        <v>96004</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -21987,7 +21987,7 @@
         <v>129675381</v>
       </c>
       <c r="B195" t="n">
-        <v>96004</v>
+        <v>96006</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -21987,7 +21987,7 @@
         <v>129675381</v>
       </c>
       <c r="B195" t="n">
-        <v>96006</v>
+        <v>96016</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -21987,7 +21987,7 @@
         <v>129675381</v>
       </c>
       <c r="B195" t="n">
-        <v>96016</v>
+        <v>96020</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -20999,7 +20999,7 @@
         <v>126668423</v>
       </c>
       <c r="B185" t="n">
-        <v>56855</v>
+        <v>56849</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -20999,7 +20999,7 @@
         <v>126668423</v>
       </c>
       <c r="B185" t="n">
-        <v>56849</v>
+        <v>56855</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2023 artfynd.xlsx
+++ b/artfynd/A 40568-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY195"/>
+  <dimension ref="A1:AY196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14235,10 +14235,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>115031254</v>
+        <v>115031352</v>
       </c>
       <c r="B126" t="n">
-        <v>74640</v>
+        <v>96604</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14247,41 +14247,37 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>308</v>
+        <v>221944</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Gransumpskog nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>685365</v>
+        <v>685317</v>
       </c>
       <c r="R126" t="n">
-        <v>6616656</v>
+        <v>6616684</v>
       </c>
       <c r="S126" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -14337,10 +14333,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>115046432</v>
+        <v>115031254</v>
       </c>
       <c r="B127" t="n">
-        <v>90350</v>
+        <v>74640</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14353,21 +14349,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5432</v>
+        <v>308</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14377,7 +14373,7 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>685381</v>
+        <v>685365</v>
       </c>
       <c r="R127" t="n">
         <v>6616656</v>
@@ -14407,12 +14403,12 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2024-03-07</t>
+          <t>2024-03-06</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2024-03-07</t>
+          <t>2024-03-06</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14439,10 +14435,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>115046040</v>
+        <v>115046432</v>
       </c>
       <c r="B128" t="n">
-        <v>90332</v>
+        <v>90350</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14455,21 +14451,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14479,7 +14475,7 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>685365</v>
+        <v>685381</v>
       </c>
       <c r="R128" t="n">
         <v>6616656</v>
@@ -14541,10 +14537,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>115137366</v>
+        <v>115046040</v>
       </c>
       <c r="B129" t="n">
-        <v>74640</v>
+        <v>90332</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14557,37 +14553,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Gransumpskog sydost om Kårsta, Upl</t>
+          <t>Gransumpskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>685394</v>
+        <v>685365</v>
       </c>
       <c r="R129" t="n">
-        <v>6616766</v>
+        <v>6616656</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14614,12 +14607,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14628,7 +14621,6 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -14647,10 +14639,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>115338429</v>
+        <v>115137366</v>
       </c>
       <c r="B130" t="n">
-        <v>90350</v>
+        <v>74640</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14663,37 +14655,40 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>5432</v>
+        <v>308</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Upl</t>
+          <t>Gransumpskog sydost om Kårsta, Upl</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>685346</v>
+        <v>685394</v>
       </c>
       <c r="R130" t="n">
-        <v>6616716</v>
+        <v>6616766</v>
       </c>
       <c r="S130" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14717,12 +14712,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14731,6 +14726,7 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -14749,10 +14745,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>115338216</v>
+        <v>115338429</v>
       </c>
       <c r="B131" t="n">
-        <v>96613</v>
+        <v>90350</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14761,25 +14757,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>221946</v>
+        <v>5432</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14789,10 +14785,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>685332</v>
+        <v>685346</v>
       </c>
       <c r="R131" t="n">
-        <v>6616685</v>
+        <v>6616716</v>
       </c>
       <c r="S131" t="n">
         <v>20</v>
@@ -14851,10 +14847,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>115699045</v>
+        <v>115338216</v>
       </c>
       <c r="B132" t="n">
-        <v>57414</v>
+        <v>96613</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14863,45 +14859,41 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>103021</v>
+        <v>221946</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Gransumpskog 1 km sydost om Kårsta, Upl</t>
+          <t>Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>685306</v>
+        <v>685332</v>
       </c>
       <c r="R132" t="n">
-        <v>6616677</v>
+        <v>6616685</v>
       </c>
       <c r="S132" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14925,12 +14917,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14957,10 +14949,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>118717859</v>
+        <v>115699045</v>
       </c>
       <c r="B133" t="n">
-        <v>98605</v>
+        <v>57414</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14973,51 +14965,41 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>222361</v>
+        <v>103021</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Barrnaturskog 750m OSO om Bergsjön (Nordväst om Tjärdalen), Upl</t>
+          <t>Gransumpskog 1 km sydost om Kårsta, Upl</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>685385</v>
+        <v>685306</v>
       </c>
       <c r="R133" t="n">
-        <v>6616774</v>
+        <v>6616677</v>
       </c>
       <c r="S133" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -15041,12 +15023,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15073,10 +15055,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120061670</v>
+        <v>118717859</v>
       </c>
       <c r="B134" t="n">
-        <v>97930</v>
+        <v>98605</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -15085,30 +15067,30 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>220787</v>
+        <v>222361</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -15118,19 +15100,19 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 750m OSO om Bergsjön (Nordväst om Tjärdalen), Upl</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>685428</v>
+        <v>685385</v>
       </c>
       <c r="R134" t="n">
-        <v>6616738</v>
+        <v>6616774</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15157,12 +15139,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15189,7 +15171,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120061796</v>
+        <v>120061670</v>
       </c>
       <c r="B135" t="n">
         <v>97930</v>
@@ -15224,7 +15206,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -15234,7 +15216,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -15243,10 +15225,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>685429</v>
+        <v>685428</v>
       </c>
       <c r="R135" t="n">
-        <v>6616759</v>
+        <v>6616738</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15279,11 +15261,6 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>En blomställning</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15310,7 +15287,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120061896</v>
+        <v>120061796</v>
       </c>
       <c r="B136" t="n">
         <v>97930</v>
@@ -15345,7 +15322,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -15355,7 +15332,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
@@ -15364,10 +15341,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>685406</v>
+        <v>685429</v>
       </c>
       <c r="R136" t="n">
-        <v>6616750</v>
+        <v>6616759</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15400,6 +15377,11 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>En blomställning</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15426,7 +15408,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120061280</v>
+        <v>120061896</v>
       </c>
       <c r="B137" t="n">
         <v>97930</v>
@@ -15461,7 +15443,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>71</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -15476,14 +15458,14 @@
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>685380</v>
+        <v>685406</v>
       </c>
       <c r="R137" t="n">
-        <v>6616654</v>
+        <v>6616750</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15542,7 +15524,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>120061391</v>
+        <v>120061280</v>
       </c>
       <c r="B138" t="n">
         <v>97930</v>
@@ -15577,7 +15559,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -15596,10 +15578,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>685384</v>
+        <v>685380</v>
       </c>
       <c r="R138" t="n">
-        <v>6616661</v>
+        <v>6616654</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15658,7 +15640,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>120061691</v>
+        <v>120061391</v>
       </c>
       <c r="B139" t="n">
         <v>97930</v>
@@ -15693,7 +15675,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -15708,14 +15690,14 @@
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>685447</v>
+        <v>685384</v>
       </c>
       <c r="R139" t="n">
-        <v>6616746</v>
+        <v>6616661</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15774,7 +15756,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>120062150</v>
+        <v>120061691</v>
       </c>
       <c r="B140" t="n">
         <v>97930</v>
@@ -15809,7 +15791,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -15819,19 +15801,19 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>685379</v>
+        <v>685447</v>
       </c>
       <c r="R140" t="n">
-        <v>6616654</v>
+        <v>6616746</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15864,11 +15846,6 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15895,7 +15872,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>120061814</v>
+        <v>120062150</v>
       </c>
       <c r="B141" t="n">
         <v>97930</v>
@@ -15930,7 +15907,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -15940,19 +15917,19 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Gransumpskog sydost om Kårsta, Gransumpskog sydost om Kårsta, Upl</t>
+          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>685421</v>
+        <v>685379</v>
       </c>
       <c r="R141" t="n">
-        <v>6616765</v>
+        <v>6616654</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15985,6 +15962,11 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16011,10 +15993,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>119812067</v>
+        <v>120061814</v>
       </c>
       <c r="B142" t="n">
-        <v>90151</v>
+        <v>97930</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -16023,41 +16005,52 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>5741</v>
+        <v>220787</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Barrnaturskog nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Gransumpskog sydost om Kårsta, Gransumpskog sydost om Kårsta, Upl</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>685340</v>
+        <v>685421</v>
       </c>
       <c r="R142" t="n">
-        <v>6616746</v>
+        <v>6616765</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16084,12 +16077,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16098,7 +16091,6 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
-      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -16117,10 +16109,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>120713578</v>
+        <v>119812067</v>
       </c>
       <c r="B143" t="n">
-        <v>91338</v>
+        <v>90151</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -16129,25 +16121,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>898</v>
+        <v>5741</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -16156,17 +16148,17 @@
       <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Kårsta byskog, Upl</t>
+          <t>Barrnaturskog nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>685300</v>
+        <v>685340</v>
       </c>
       <c r="R143" t="n">
-        <v>6616654</v>
+        <v>6616746</v>
       </c>
       <c r="S143" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -16190,17 +16182,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>Exkursion med Botaniska Sällskapet i Sthlm samt Naturskyddsföreningen Vallentuna.</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16213,45 +16200,25 @@
       <c r="AG143" t="b">
         <v>0</v>
       </c>
-      <c r="AH143" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
-      </c>
-      <c r="AJ143" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK143" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO143" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Lisel Hamring</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Lisel Hamring</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>120742091</v>
+        <v>120713578</v>
       </c>
       <c r="B144" t="n">
-        <v>98059</v>
+        <v>91338</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16264,51 +16231,40 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>220787</v>
+        <v>898</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Kårsta byskog, Upl</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>685249</v>
+        <v>685300</v>
       </c>
       <c r="R144" t="n">
-        <v>6616652</v>
+        <v>6616654</v>
       </c>
       <c r="S144" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -16332,12 +16288,17 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-27</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-27</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>Exkursion med Botaniska Sällskapet i Sthlm samt Naturskyddsföreningen Vallentuna.</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16346,25 +16307,46 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
+      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
+      </c>
+      <c r="AH144" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
+      </c>
+      <c r="AJ144" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK144" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO144" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Lisel Hamring</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Lisel Hamring</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>120742594</v>
+        <v>120742091</v>
       </c>
       <c r="B145" t="n">
         <v>98059</v>
@@ -16399,7 +16381,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -16409,7 +16391,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -16418,10 +16400,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>685278</v>
+        <v>685249</v>
       </c>
       <c r="R145" t="n">
-        <v>6616713</v>
+        <v>6616652</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16454,11 +16436,6 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2024-10-29</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>2 blomställningar</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16485,10 +16462,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>120741868</v>
+        <v>120742594</v>
       </c>
       <c r="B146" t="n">
-        <v>98157</v>
+        <v>98059</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16520,7 +16497,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -16530,21 +16507,19 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Barrnaturskog nordväst om Tjärdalen, Barrnaturskog nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>685307</v>
+        <v>685278</v>
       </c>
       <c r="R146" t="n">
-        <v>6616649</v>
+        <v>6616713</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16579,13 +16554,17 @@
           <t>2024-10-29</t>
         </is>
       </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>2 blomställningar</t>
+        </is>
+      </c>
       <c r="AD146" t="b">
         <v>0</v>
       </c>
       <c r="AE146" t="b">
         <v>0</v>
       </c>
-      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
@@ -16604,10 +16583,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>120742485</v>
+        <v>120741868</v>
       </c>
       <c r="B147" t="n">
-        <v>98059</v>
+        <v>98157</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16652,16 +16631,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog nordväst om Tjärdalen, Barrnaturskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>685276</v>
+        <v>685307</v>
       </c>
       <c r="R147" t="n">
-        <v>6616670</v>
+        <v>6616649</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16702,6 +16683,7 @@
       <c r="AE147" t="b">
         <v>0</v>
       </c>
+      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
       </c>
@@ -16720,7 +16702,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>120742626</v>
+        <v>120742485</v>
       </c>
       <c r="B148" t="n">
         <v>98059</v>
@@ -16755,7 +16737,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -16765,7 +16747,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
@@ -16774,10 +16756,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>685263</v>
+        <v>685276</v>
       </c>
       <c r="R148" t="n">
-        <v>6616724</v>
+        <v>6616670</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16836,7 +16818,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>120742252</v>
+        <v>120742626</v>
       </c>
       <c r="B149" t="n">
         <v>98059</v>
@@ -16871,7 +16853,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -16881,21 +16863,19 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>685253</v>
+        <v>685263</v>
       </c>
       <c r="R149" t="n">
-        <v>6616665</v>
+        <v>6616724</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16936,7 +16916,6 @@
       <c r="AE149" t="b">
         <v>0</v>
       </c>
-      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
@@ -16955,10 +16934,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>120741991</v>
+        <v>120742252</v>
       </c>
       <c r="B150" t="n">
-        <v>98157</v>
+        <v>98059</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16990,7 +16969,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -17007,14 +16986,14 @@
       <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Gransumpskog 1 km sydost om Kårsta, Gransumpskog 1 km sydost om Kårsta, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>685302</v>
+        <v>685253</v>
       </c>
       <c r="R150" t="n">
-        <v>6616679</v>
+        <v>6616665</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17074,10 +17053,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>120759925</v>
+        <v>120741991</v>
       </c>
       <c r="B151" t="n">
-        <v>98071</v>
+        <v>98157</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17109,7 +17088,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -17122,16 +17101,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Gransumpskog 1 km sydost om Kårsta, Gransumpskog 1 km sydost om Kårsta, Upl</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>685296</v>
+        <v>685302</v>
       </c>
       <c r="R151" t="n">
-        <v>6616725</v>
+        <v>6616679</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17158,12 +17139,12 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17172,6 +17153,7 @@
       <c r="AE151" t="b">
         <v>0</v>
       </c>
+      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
@@ -17190,7 +17172,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>120760778</v>
+        <v>120759925</v>
       </c>
       <c r="B152" t="n">
         <v>98071</v>
@@ -17225,7 +17207,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -17244,10 +17226,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>685370</v>
+        <v>685296</v>
       </c>
       <c r="R152" t="n">
-        <v>6616785</v>
+        <v>6616725</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17306,7 +17288,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>120760174</v>
+        <v>120760778</v>
       </c>
       <c r="B153" t="n">
         <v>98071</v>
@@ -17341,7 +17323,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -17354,18 +17336,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>685346</v>
+        <v>685370</v>
       </c>
       <c r="R153" t="n">
-        <v>6616758</v>
+        <v>6616785</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17406,7 +17386,6 @@
       <c r="AE153" t="b">
         <v>0</v>
       </c>
-      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
@@ -17425,7 +17404,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>120759986</v>
+        <v>120760174</v>
       </c>
       <c r="B154" t="n">
         <v>98071</v>
@@ -17460,7 +17439,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -17473,16 +17452,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>685342</v>
+        <v>685346</v>
       </c>
       <c r="R154" t="n">
-        <v>6616736</v>
+        <v>6616758</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17523,6 +17504,7 @@
       <c r="AE154" t="b">
         <v>0</v>
       </c>
+      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
       </c>
@@ -17541,7 +17523,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>120759914</v>
+        <v>120759986</v>
       </c>
       <c r="B155" t="n">
         <v>98071</v>
@@ -17576,7 +17558,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -17595,10 +17577,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>685311</v>
+        <v>685342</v>
       </c>
       <c r="R155" t="n">
-        <v>6616724</v>
+        <v>6616736</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17657,10 +17639,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>120761028</v>
+        <v>120759914</v>
       </c>
       <c r="B156" t="n">
-        <v>98157</v>
+        <v>98071</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17692,7 +17674,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>213</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -17705,18 +17687,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L156" t="inlineStr"/>
-      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>685433</v>
+        <v>685311</v>
       </c>
       <c r="R156" t="n">
-        <v>6616678</v>
+        <v>6616724</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17743,12 +17723,12 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17757,7 +17737,6 @@
       <c r="AE156" t="b">
         <v>0</v>
       </c>
-      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
@@ -17776,10 +17755,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>120761260</v>
+        <v>120761028</v>
       </c>
       <c r="B157" t="n">
-        <v>98071</v>
+        <v>98157</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17811,7 +17790,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -17824,16 +17803,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>685438</v>
+        <v>685433</v>
       </c>
       <c r="R157" t="n">
-        <v>6616696</v>
+        <v>6616678</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17860,12 +17841,12 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-12-25</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-12-25</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17874,6 +17855,7 @@
       <c r="AE157" t="b">
         <v>0</v>
       </c>
+      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
@@ -17892,7 +17874,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>120760861</v>
+        <v>120761260</v>
       </c>
       <c r="B158" t="n">
         <v>98071</v>
@@ -17927,7 +17909,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -17946,10 +17928,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>685381</v>
+        <v>685438</v>
       </c>
       <c r="R158" t="n">
-        <v>6616734</v>
+        <v>6616696</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18008,7 +17990,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>120760830</v>
+        <v>120760861</v>
       </c>
       <c r="B159" t="n">
         <v>98071</v>
@@ -18043,7 +18025,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -18062,10 +18044,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>685374</v>
+        <v>685381</v>
       </c>
       <c r="R159" t="n">
-        <v>6616755</v>
+        <v>6616734</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18124,7 +18106,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>120760736</v>
+        <v>120760830</v>
       </c>
       <c r="B160" t="n">
         <v>98071</v>
@@ -18159,7 +18141,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -18169,7 +18151,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
@@ -18178,10 +18160,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>685370</v>
+        <v>685374</v>
       </c>
       <c r="R160" t="n">
-        <v>6616803</v>
+        <v>6616755</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18214,11 +18196,6 @@
       <c r="AA160" t="inlineStr">
         <is>
           <t>2024-10-30</t>
-        </is>
-      </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>1 blomställning</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18245,10 +18222,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>120836325</v>
+        <v>120760736</v>
       </c>
       <c r="B161" t="n">
-        <v>98098</v>
+        <v>98071</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -18280,7 +18257,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -18290,19 +18267,19 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Barrnaturskog nordväst om Tjärdalen, Barrnaturskog nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>685314</v>
+        <v>685370</v>
       </c>
       <c r="R161" t="n">
-        <v>6616738</v>
+        <v>6616803</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18329,12 +18306,17 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>1 blomställning</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18361,10 +18343,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121343884</v>
+        <v>120836325</v>
       </c>
       <c r="B162" t="n">
-        <v>97059</v>
+        <v>98098</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18373,38 +18355,52 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>224361</v>
+        <v>220787</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Björk</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog nordväst om Tjärdalen, Barrnaturskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>685317</v>
+        <v>685314</v>
       </c>
       <c r="R162" t="n">
-        <v>6616676</v>
+        <v>6616738</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18431,12 +18427,12 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18463,10 +18459,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121567592</v>
+        <v>121343884</v>
       </c>
       <c r="B163" t="n">
-        <v>8436</v>
+        <v>97059</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -18479,39 +18475,34 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>106545</v>
+        <v>224361</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
-      <c r="M163" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Gransumpskog nordväst om Tjärdalen, Gransumpskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>685437</v>
+        <v>685317</v>
       </c>
       <c r="R163" t="n">
-        <v>6616649</v>
+        <v>6616676</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18538,12 +18529,12 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18570,10 +18561,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121735325</v>
+        <v>121567592</v>
       </c>
       <c r="B164" t="n">
-        <v>98157</v>
+        <v>8436</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -18582,54 +18573,43 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>685448</v>
+        <v>685437</v>
       </c>
       <c r="R164" t="n">
-        <v>6616789</v>
+        <v>6616649</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18656,12 +18636,12 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18670,7 +18650,6 @@
       <c r="AE164" t="b">
         <v>0</v>
       </c>
-      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
@@ -18689,7 +18668,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121734849</v>
+        <v>121735325</v>
       </c>
       <c r="B165" t="n">
         <v>98157</v>
@@ -18724,7 +18703,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -18737,16 +18716,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>685480</v>
+        <v>685448</v>
       </c>
       <c r="R165" t="n">
-        <v>6616744</v>
+        <v>6616789</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18787,6 +18768,7 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
+      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
@@ -18805,7 +18787,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121735531</v>
+        <v>121734849</v>
       </c>
       <c r="B166" t="n">
         <v>98157</v>
@@ -18840,7 +18822,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -18859,10 +18841,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>685357</v>
+        <v>685480</v>
       </c>
       <c r="R166" t="n">
-        <v>6616798</v>
+        <v>6616744</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18921,10 +18903,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121733071</v>
+        <v>121735531</v>
       </c>
       <c r="B167" t="n">
-        <v>90781</v>
+        <v>98157</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18933,38 +18915,52 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>685246</v>
+        <v>685357</v>
       </c>
       <c r="R167" t="n">
-        <v>6616659</v>
+        <v>6616798</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19023,10 +19019,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121735485</v>
+        <v>121733071</v>
       </c>
       <c r="B168" t="n">
-        <v>98157</v>
+        <v>90781</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -19035,54 +19031,38 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L168" t="inlineStr"/>
-      <c r="N168" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>685409</v>
+        <v>685246</v>
       </c>
       <c r="R168" t="n">
-        <v>6616795</v>
+        <v>6616659</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19117,18 +19097,12 @@
           <t>2024-12-25</t>
         </is>
       </c>
-      <c r="AC168" t="inlineStr">
-        <is>
-          <t>4 blomställningar</t>
-        </is>
-      </c>
       <c r="AD168" t="b">
         <v>0</v>
       </c>
       <c r="AE168" t="b">
         <v>0</v>
       </c>
-      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
@@ -19147,7 +19121,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>121735377</v>
+        <v>121735485</v>
       </c>
       <c r="B169" t="n">
         <v>98157</v>
@@ -19182,7 +19156,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>78</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -19192,19 +19166,21 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>685440</v>
+        <v>685409</v>
       </c>
       <c r="R169" t="n">
-        <v>6616805</v>
+        <v>6616795</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19239,12 +19215,18 @@
           <t>2024-12-25</t>
         </is>
       </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>4 blomställningar</t>
+        </is>
+      </c>
       <c r="AD169" t="b">
         <v>0</v>
       </c>
       <c r="AE169" t="b">
         <v>0</v>
       </c>
+      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
@@ -19263,7 +19245,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>121735498</v>
+        <v>121735377</v>
       </c>
       <c r="B170" t="n">
         <v>98157</v>
@@ -19298,7 +19280,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -19317,10 +19299,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>685410</v>
+        <v>685440</v>
       </c>
       <c r="R170" t="n">
-        <v>6616808</v>
+        <v>6616805</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19379,7 +19361,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>121734727</v>
+        <v>121735498</v>
       </c>
       <c r="B171" t="n">
         <v>98157</v>
@@ -19414,7 +19396,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -19427,18 +19409,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L171" t="inlineStr"/>
-      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>685481</v>
+        <v>685410</v>
       </c>
       <c r="R171" t="n">
-        <v>6616734</v>
+        <v>6616808</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19479,7 +19459,6 @@
       <c r="AE171" t="b">
         <v>0</v>
       </c>
-      <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="b">
         <v>0</v>
       </c>
@@ -19498,7 +19477,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121735074</v>
+        <v>121734727</v>
       </c>
       <c r="B172" t="n">
         <v>98157</v>
@@ -19533,7 +19512,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -19546,16 +19525,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>685486</v>
+        <v>685481</v>
       </c>
       <c r="R172" t="n">
-        <v>6616781</v>
+        <v>6616734</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19596,6 +19577,7 @@
       <c r="AE172" t="b">
         <v>0</v>
       </c>
+      <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="b">
         <v>0</v>
       </c>
@@ -19614,7 +19596,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>121735416</v>
+        <v>121735074</v>
       </c>
       <c r="B173" t="n">
         <v>98157</v>
@@ -19649,7 +19631,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -19668,10 +19650,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>685413</v>
+        <v>685486</v>
       </c>
       <c r="R173" t="n">
-        <v>6616793</v>
+        <v>6616781</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19730,7 +19712,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>121734887</v>
+        <v>121735416</v>
       </c>
       <c r="B174" t="n">
         <v>98157</v>
@@ -19765,7 +19747,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -19784,10 +19766,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>685475</v>
+        <v>685413</v>
       </c>
       <c r="R174" t="n">
-        <v>6616757</v>
+        <v>6616793</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19846,7 +19828,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>121743769</v>
+        <v>121734887</v>
       </c>
       <c r="B175" t="n">
         <v>98157</v>
@@ -19881,7 +19863,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -19894,18 +19876,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>685401</v>
+        <v>685475</v>
       </c>
       <c r="R175" t="n">
-        <v>6616722</v>
+        <v>6616757</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19932,17 +19912,12 @@
       </c>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-12-25</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
-        </is>
-      </c>
-      <c r="AC175" t="inlineStr">
-        <is>
-          <t>Återbesök</t>
+          <t>2024-12-25</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19951,7 +19926,6 @@
       <c r="AE175" t="b">
         <v>0</v>
       </c>
-      <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="b">
         <v>0</v>
       </c>
@@ -19970,7 +19944,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>121735053</v>
+        <v>121743769</v>
       </c>
       <c r="B176" t="n">
         <v>98157</v>
@@ -20005,7 +19979,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -20015,7 +19989,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L176" t="inlineStr"/>
@@ -20026,10 +20000,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>685473</v>
+        <v>685401</v>
       </c>
       <c r="R176" t="n">
-        <v>6616791</v>
+        <v>6616722</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -20056,17 +20030,17 @@
       </c>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>2024-12-25</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>En blomställning</t>
+          <t>Återbesök</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -20094,7 +20068,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>121734526</v>
+        <v>121735053</v>
       </c>
       <c r="B177" t="n">
         <v>98157</v>
@@ -20129,7 +20103,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>242</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -20139,7 +20113,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L177" t="inlineStr"/>
@@ -20150,10 +20124,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>685452</v>
+        <v>685473</v>
       </c>
       <c r="R177" t="n">
-        <v>6616694</v>
+        <v>6616791</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -20190,7 +20164,7 @@
       </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>Återbesök. Kring en äldre tall.</t>
+          <t>En blomställning</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20218,10 +20192,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>121762495</v>
+        <v>121734526</v>
       </c>
       <c r="B178" t="n">
-        <v>90781</v>
+        <v>98157</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -20230,38 +20204,54 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>685252</v>
+        <v>685452</v>
       </c>
       <c r="R178" t="n">
-        <v>6616654</v>
+        <v>6616694</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20288,12 +20278,17 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2024-12-25</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2024-12-25</t>
+        </is>
+      </c>
+      <c r="AC178" t="inlineStr">
+        <is>
+          <t>Återbesök. Kring en äldre tall.</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -20302,6 +20297,7 @@
       <c r="AE178" t="b">
         <v>0</v>
       </c>
+      <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="b">
         <v>0</v>
       </c>
@@ -20320,10 +20316,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>122380531</v>
+        <v>121762495</v>
       </c>
       <c r="B179" t="n">
-        <v>94760</v>
+        <v>90781</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -20332,38 +20328,38 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>2813</v>
+        <v>5432</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Barrnaturskog 800m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>685355</v>
+        <v>685252</v>
       </c>
       <c r="R179" t="n">
-        <v>6616740</v>
+        <v>6616654</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20390,12 +20386,12 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20422,10 +20418,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>122775468</v>
+        <v>122380531</v>
       </c>
       <c r="B180" t="n">
-        <v>98376</v>
+        <v>94760</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -20434,55 +20430,41 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>220787</v>
+        <v>2813</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J180" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="N180" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Myran, Myran, Upl</t>
+          <t>Barrnaturskog 800m sydost om Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>685395</v>
+        <v>685355</v>
       </c>
       <c r="R180" t="n">
-        <v>6616688</v>
+        <v>6616740</v>
       </c>
       <c r="S180" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -20506,27 +20488,12 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="Z180" t="inlineStr">
-        <is>
-          <t>13:21</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AB180" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
-      <c r="AC180" t="inlineStr">
-        <is>
-          <t>Mellan 50 och 100 plantor växte mycket tätt nära en stig. Medobservatör: Beatrice Hymnelius.</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -20541,22 +20508,22 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Carl-Oscar  Rohwer</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Carl-Oscar  Rohwer</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>123282824</v>
+        <v>122775468</v>
       </c>
       <c r="B181" t="n">
-        <v>57644</v>
+        <v>98376</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -20565,50 +20532,55 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m SO Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Myran, Myran, Upl</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>685357</v>
+        <v>685395</v>
       </c>
       <c r="R181" t="n">
-        <v>6616766</v>
+        <v>6616688</v>
       </c>
       <c r="S181" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -20632,12 +20604,27 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="Z181" t="inlineStr">
+        <is>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AB181" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t>Mellan 50 och 100 plantor växte mycket tätt nära en stig. Medobservatör: Beatrice Hymnelius.</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -20652,22 +20639,22 @@
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Carl-Oscar  Rohwer</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Carl-Oscar  Rohwer</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>123282215</v>
+        <v>123282824</v>
       </c>
       <c r="B182" t="n">
-        <v>74887</v>
+        <v>57644</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -20676,44 +20663,50 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>306</v>
+        <v>103021</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr"/>
-      <c r="J182" t="inlineStr"/>
-      <c r="K182" t="inlineStr"/>
-      <c r="N182" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Barrnaturskog 800m SO Bergsjön , Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m SO Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>685329</v>
+        <v>685357</v>
       </c>
       <c r="R182" t="n">
-        <v>6616644</v>
+        <v>6616766</v>
       </c>
       <c r="S182" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -20751,7 +20744,6 @@
       <c r="AE182" t="b">
         <v>0</v>
       </c>
-      <c r="AF182" t="inlineStr"/>
       <c r="AG182" t="b">
         <v>0</v>
       </c>
@@ -20770,10 +20762,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>123662940</v>
+        <v>123282215</v>
       </c>
       <c r="B183" t="n">
-        <v>95551</v>
+        <v>74887</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -20786,35 +20778,26 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>210</v>
+        <v>306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J183" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr"/>
-      <c r="L183" t="inlineStr"/>
       <c r="N183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
@@ -20822,10 +20805,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>685438</v>
+        <v>685329</v>
       </c>
       <c r="R183" t="n">
-        <v>6616703</v>
+        <v>6616644</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20852,12 +20835,12 @@
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -20885,10 +20868,15 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>125443813</v>
+        <v>123662940</v>
       </c>
       <c r="B184" t="n">
-        <v>98362</v>
+        <v>95551</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20896,48 +20884,46 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>221952</v>
+        <v>210</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
+      <c r="N184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Barrnaturskog nordväst om Tjärdalen, Barrnaturskog nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 800m SO Bergsjön , Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>685328</v>
+        <v>685438</v>
       </c>
       <c r="R184" t="n">
-        <v>6616664</v>
+        <v>6616703</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20964,12 +20950,12 @@
       </c>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -20978,6 +20964,7 @@
       <c r="AE184" t="b">
         <v>0</v>
       </c>
+      <c r="AF184" t="inlineStr"/>
       <c r="AG184" t="b">
         <v>0</v>
       </c>
@@ -20996,10 +20983,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>126668423</v>
+        <v>125443813</v>
       </c>
       <c r="B185" t="n">
-        <v>56855</v>
+        <v>98362</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21007,21 +20994,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>100138</v>
+        <v>221952</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -21029,23 +21016,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
-      <c r="L185" t="inlineStr"/>
-      <c r="M185" t="inlineStr"/>
-      <c r="N185" t="inlineStr"/>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Kårstabyskogen, Upl</t>
+          <t>Barrnaturskog nordväst om Tjärdalen, Barrnaturskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>685285</v>
+        <v>685328</v>
       </c>
       <c r="R185" t="n">
-        <v>6616727</v>
+        <v>6616664</v>
       </c>
       <c r="S185" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -21069,12 +21062,12 @@
       </c>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -21101,10 +21094,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>127043186</v>
+        <v>126668423</v>
       </c>
       <c r="B186" t="n">
-        <v>95822</v>
+        <v>56855</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21112,37 +21105,45 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>2818</v>
+        <v>100138</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" t="inlineStr"/>
+      <c r="N186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Gransumpskog 700m OSO Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Kårstabyskogen, Upl</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>685389</v>
+        <v>685285</v>
       </c>
       <c r="R186" t="n">
-        <v>6616746</v>
+        <v>6616727</v>
       </c>
       <c r="S186" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -21166,12 +21167,12 @@
       </c>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -21198,10 +21199,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>128610913</v>
+        <v>127043186</v>
       </c>
       <c r="B187" t="n">
-        <v>95885</v>
+        <v>95822</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21209,34 +21210,34 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>2809</v>
+        <v>2818</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Barrnaturskog 700m O Bergsjön, Nordväst om Tjärdalen, Upl</t>
+          <t>Gransumpskog 700m OSO Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>685398</v>
+        <v>685389</v>
       </c>
       <c r="R187" t="n">
-        <v>6616729</v>
+        <v>6616746</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21263,12 +21264,12 @@
       </c>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -21295,10 +21296,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>128611241</v>
+        <v>128610913</v>
       </c>
       <c r="B188" t="n">
-        <v>91035</v>
+        <v>95885</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -21306,21 +21307,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>5741</v>
+        <v>2809</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -21330,10 +21331,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>685420</v>
+        <v>685398</v>
       </c>
       <c r="R188" t="n">
-        <v>6616725</v>
+        <v>6616729</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21392,7 +21393,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>128611191</v>
+        <v>128611241</v>
       </c>
       <c r="B189" t="n">
         <v>91035</v>
@@ -21427,10 +21428,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>685428</v>
+        <v>685420</v>
       </c>
       <c r="R189" t="n">
-        <v>6616695</v>
+        <v>6616725</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21489,51 +21490,42 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128611218</v>
+        <v>128611191</v>
       </c>
       <c r="B190" t="n">
-        <v>92808</v>
+        <v>91035</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>150</v>
+        <v>5741</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m O Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>685426</v>
+        <v>685428</v>
       </c>
       <c r="R190" t="n">
         <v>6616695</v>
@@ -21569,11 +21561,6 @@
       <c r="AA190" t="inlineStr">
         <is>
           <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="AC190" t="inlineStr">
-        <is>
-          <t>Återfynd</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -21600,45 +21587,54 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>128610942</v>
+        <v>128611218</v>
       </c>
       <c r="B191" t="n">
-        <v>91299</v>
+        <v>92808</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>3215</v>
+        <v>150</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr"/>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P191" t="inlineStr">
         <is>
           <t>Barrnaturskog 700m O Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>685398</v>
+        <v>685426</v>
       </c>
       <c r="R191" t="n">
-        <v>6616729</v>
+        <v>6616695</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21671,6 +21667,11 @@
       <c r="AA191" t="inlineStr">
         <is>
           <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC191" t="inlineStr">
+        <is>
+          <t>Återfynd</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -21697,10 +21698,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>128611030</v>
+        <v>128610942</v>
       </c>
       <c r="B192" t="n">
-        <v>87047</v>
+        <v>91299</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21708,19 +21709,23 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>3624</v>
+        <v>3215</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H192" t="inlineStr"/>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
       <c r="I192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
@@ -21728,10 +21733,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>685411</v>
+        <v>685398</v>
       </c>
       <c r="R192" t="n">
-        <v>6616715</v>
+        <v>6616729</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21790,10 +21795,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>128629864</v>
+        <v>128611030</v>
       </c>
       <c r="B193" t="n">
-        <v>86961</v>
+        <v>87047</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21801,34 +21806,30 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>1988</v>
+        <v>3624</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
-        </is>
-      </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>Fr.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
+          <t>Barrnaturskog 700m O Bergsjön, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>685354</v>
+        <v>685411</v>
       </c>
       <c r="R193" t="n">
-        <v>6616772</v>
+        <v>6616715</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21855,12 +21856,12 @@
       </c>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21887,45 +21888,45 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129184200</v>
+        <v>128629864</v>
       </c>
       <c r="B194" t="n">
-        <v>91805</v>
+        <v>86961</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>1106</v>
+        <v>1988</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Barrnaturskog nordväst om Tjärdalen, Barrnaturskog nordväst om Tjärdalen, Upl</t>
+          <t>Nordväst om Tjärdalen, Nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>685322</v>
+        <v>685354</v>
       </c>
       <c r="R194" t="n">
-        <v>6616694</v>
+        <v>6616772</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21952,12 +21953,12 @@
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21984,45 +21985,45 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129675381</v>
+        <v>129184200</v>
       </c>
       <c r="B195" t="n">
-        <v>96046</v>
+        <v>91805</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>2809</v>
+        <v>1106</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Kårstabyskogen, Upl</t>
+          <t>Barrnaturskog nordväst om Tjärdalen, Barrnaturskog nordväst om Tjärdalen, Upl</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>685347</v>
+        <v>685322</v>
       </c>
       <c r="R195" t="n">
-        <v>6616663</v>
+        <v>6616694</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -22049,12 +22050,12 @@
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -22063,7 +22064,6 @@
       <c r="AE195" t="b">
         <v>0</v>
       </c>
-      <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="b">
         <v>0</v>
       </c>
@@ -22079,6 +22079,104 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>129675381</v>
+      </c>
+      <c r="B196" t="n">
+        <v>96046</v>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr"/>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>Kårstabyskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q196" t="n">
+        <v>685347</v>
+      </c>
+      <c r="R196" t="n">
+        <v>6616663</v>
+      </c>
+      <c r="S196" t="n">
+        <v>10</v>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W196" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y196" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF196" t="inlineStr"/>
+      <c r="AG196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT196" t="inlineStr"/>
+      <c r="AW196" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX196" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY196" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
